--- a/model/Outputs/11. Interest rate/30/Output Files/0.3/Output_6_39.xlsx
+++ b/model/Outputs/11. Interest rate/30/Output Files/0.3/Output_6_39.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2251481.55099216</v>
+        <v>2244452.290314603</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9630586.08125224</v>
+        <v>9630586.081252653</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9630586.08125224</v>
+        <v>9630586.081252653</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>168741.8430705665</v>
+        <v>168741.843070663</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>168741.8430705665</v>
+        <v>168741.843070663</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16968380.29632899</v>
+        <v>16968380.29632898</v>
       </c>
     </row>
   </sheetData>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>250.414304340989</v>
+        <v>81.99931295557451</v>
       </c>
       <c r="C2" t="n">
         <v>49.47457824299391</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>168.4149913854146</v>
       </c>
       <c r="S2" t="n">
         <v>94.84816780232291</v>
@@ -736,7 +736,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>199.8180013219742</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -748,10 +748,10 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -778,19 +778,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R3" t="n">
         <v>147.2737972923793</v>
       </c>
       <c r="S3" t="n">
-        <v>66.5639999646113</v>
+        <v>421</v>
       </c>
       <c r="T3" t="n">
         <v>5.357765217513816</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2103597601867477</v>
+        <v>330.4207190177412</v>
       </c>
       <c r="V3" t="n">
         <v>14.51066719152016</v>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>175.4172848236332</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1015,10 +1015,10 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>421</v>
+        <v>147.2737972923793</v>
       </c>
       <c r="S6" t="n">
         <v>66.5639999646113</v>
@@ -1030,7 +1030,7 @@
         <v>0.2103597601867477</v>
       </c>
       <c r="V6" t="n">
-        <v>77.49313687914002</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W6" t="n">
         <v>32.37314290982852</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>81.99931295557451</v>
+        <v>250.414304340989</v>
       </c>
       <c r="C8" t="n">
         <v>49.47457824299391</v>
@@ -1188,7 +1188,7 @@
         <v>249.2212965486107</v>
       </c>
       <c r="V8" t="n">
-        <v>398.2660155522383</v>
+        <v>229.8510241668239</v>
       </c>
       <c r="W8" t="n">
         <v>238.3734759809475</v>
@@ -1252,13 +1252,13 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>147.2737972923793</v>
+        <v>421</v>
       </c>
       <c r="S9" t="n">
-        <v>362.5835021673831</v>
+        <v>66.5639999646113</v>
       </c>
       <c r="T9" t="n">
         <v>5.357765217513816</v>
@@ -1270,10 +1270,10 @@
         <v>14.51066719152016</v>
       </c>
       <c r="W9" t="n">
-        <v>421</v>
+        <v>216.3725645856306</v>
       </c>
       <c r="X9" t="n">
-        <v>19.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1456,10 +1456,10 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>86.93822665041522</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1492,10 +1492,10 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>547.2737972923793</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S12" t="n">
-        <v>179.2417624900537</v>
+        <v>116.5639999646113</v>
       </c>
       <c r="T12" t="n">
         <v>55.35776521751382</v>
@@ -1614,7 +1614,7 @@
         <v>54.36328960686865</v>
       </c>
       <c r="F14" t="n">
-        <v>54.88962870801186</v>
+        <v>58.85502009342638</v>
       </c>
       <c r="G14" t="n">
         <v>53.75737228701621</v>
@@ -1653,7 +1653,7 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>148.8135591877373</v>
+        <v>144.8481678023229</v>
       </c>
       <c r="T14" t="n">
         <v>236.6755817285639</v>
@@ -1690,16 +1690,16 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>73.04152018756569</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>80.50967533902147</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1887,10 +1887,10 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S17" t="n">
-        <v>148.8135591877373</v>
+        <v>144.8481678023229</v>
       </c>
       <c r="T17" t="n">
         <v>236.6755817285639</v>
@@ -1921,16 +1921,16 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C18" t="n">
-        <v>11.09991244551929</v>
+        <v>73.77767497096173</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>73.04152018756569</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1966,7 +1966,7 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>197.2737972923793</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S18" t="n">
         <v>116.5639999646113</v>
@@ -2124,10 +2124,10 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>144.8481678023229</v>
+        <v>148.8135591877373</v>
       </c>
       <c r="T20" t="n">
         <v>236.6755817285639</v>
@@ -2161,7 +2161,7 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D21" t="n">
-        <v>62.67776252544243</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -2206,7 +2206,7 @@
         <v>547.2737972923793</v>
       </c>
       <c r="S21" t="n">
-        <v>116.5639999646113</v>
+        <v>179.2417624900537</v>
       </c>
       <c r="T21" t="n">
         <v>55.35776521751382</v>
@@ -2331,7 +2331,7 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H23" t="n">
-        <v>58.00965870352741</v>
+        <v>61.97505008894191</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>144.8481678023229</v>
@@ -2395,7 +2395,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C24" t="n">
-        <v>361.0999124455193</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -2407,10 +2407,10 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>86.93822665041519</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2440,7 +2440,7 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>259.9515598178218</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S24" t="n">
         <v>116.5639999646113</v>
@@ -2562,7 +2562,7 @@
         <v>93.36328960686865</v>
       </c>
       <c r="F26" t="n">
-        <v>87.40542009371138</v>
+        <v>93.88962870801186</v>
       </c>
       <c r="G26" t="n">
         <v>92.75737228701621</v>
@@ -2616,7 +2616,7 @@
         <v>327.3734759809475</v>
       </c>
       <c r="X26" t="n">
-        <v>281.2818334606677</v>
+        <v>274.7976248460823</v>
       </c>
       <c r="Y26" t="n">
         <v>200.3174326828064</v>
@@ -2799,7 +2799,7 @@
         <v>93.36328960686865</v>
       </c>
       <c r="F29" t="n">
-        <v>87.40542009362946</v>
+        <v>93.88962870801186</v>
       </c>
       <c r="G29" t="n">
         <v>92.75737228701621</v>
@@ -2838,7 +2838,7 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>183.8481678023229</v>
+        <v>177.3639591880256</v>
       </c>
       <c r="T29" t="n">
         <v>275.6755817285639</v>
@@ -2978,25 +2978,25 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>209.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>260.1850752716849</v>
+        <v>133.391197361505</v>
       </c>
       <c r="O31" t="n">
         <v>329.445564079015</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>376.4478973282775</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>414.839266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>415.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>39.25954645999447</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3036,7 +3036,7 @@
         <v>93.36328960686865</v>
       </c>
       <c r="F32" t="n">
-        <v>93.88962870801186</v>
+        <v>87.40542009342639</v>
       </c>
       <c r="G32" t="n">
         <v>92.75737228701621</v>
@@ -3075,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>177.3639591880224</v>
+        <v>183.8481678023229</v>
       </c>
       <c r="T32" t="n">
         <v>275.6755817285639</v>
@@ -3212,25 +3212,25 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>112.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>209.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>260.1850752716849</v>
+        <v>132.6283358059518</v>
       </c>
       <c r="O34" t="n">
         <v>329.445564079015</v>
       </c>
       <c r="P34" t="n">
-        <v>342.3140462833665</v>
+        <v>376.4478973282775</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>415.6021279811511</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -3282,7 +3282,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I35" t="n">
-        <v>3.96539138569952</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3324,7 +3324,7 @@
         <v>279.8510241668239</v>
       </c>
       <c r="W35" t="n">
-        <v>288.3734759809475</v>
+        <v>292.3388673663621</v>
       </c>
       <c r="X35" t="n">
         <v>242.2818334606677</v>
@@ -3343,7 +3343,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C36" t="n">
-        <v>11.09991244551929</v>
+        <v>73.77767497096178</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -3358,7 +3358,7 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -3400,13 +3400,13 @@
         <v>50.21035976018675</v>
       </c>
       <c r="V36" t="n">
-        <v>64.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W36" t="n">
         <v>82.37314290982852</v>
       </c>
       <c r="X36" t="n">
-        <v>150.372414784409</v>
+        <v>69.86273944538755</v>
       </c>
       <c r="Y36" t="n">
         <v>49.39139276613435</v>
@@ -3516,7 +3516,7 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H38" t="n">
-        <v>61.97505008922693</v>
+        <v>58.00965870352741</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3549,7 +3549,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>144.8481678023229</v>
+        <v>148.8135591877373</v>
       </c>
       <c r="T38" t="n">
         <v>236.6755817285639</v>
@@ -3583,13 +3583,13 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>62.67776252544243</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>239.5984974349628</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -3622,7 +3622,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>197.2737972923793</v>
@@ -3640,7 +3640,7 @@
         <v>64.51066719152016</v>
       </c>
       <c r="W39" t="n">
-        <v>82.37314290982852</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X39" t="n">
         <v>69.86273944538755</v>
@@ -3753,10 +3753,10 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H41" t="n">
-        <v>58.00965870352741</v>
+        <v>61.97505008894191</v>
       </c>
       <c r="I41" t="n">
-        <v>3.96539138569952</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3826,7 +3826,7 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>64.74007562773993</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -3862,7 +3862,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>262.0138729201192</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S42" t="n">
         <v>116.5639999646113</v>
@@ -3987,13 +3987,13 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G44" t="n">
-        <v>57.72276367271574</v>
+        <v>53.75737228701621</v>
       </c>
       <c r="H44" t="n">
         <v>58.00965870352741</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4060,13 +4060,13 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>342.6720972219126</v>
+        <v>62.67776252544243</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>70.00566530352997</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>197.2737972923793</v>
       </c>
       <c r="S45" t="n">
-        <v>116.5639999646113</v>
+        <v>466.5639999646113</v>
       </c>
       <c r="T45" t="n">
         <v>55.35776521751382</v>
@@ -4321,52 +4321,52 @@
         <v>33.68</v>
       </c>
       <c r="J2" t="n">
-        <v>33.68</v>
+        <v>424.9891130376557</v>
       </c>
       <c r="K2" t="n">
-        <v>33.68</v>
+        <v>424.9891130376557</v>
       </c>
       <c r="L2" t="n">
-        <v>33.68</v>
+        <v>424.9891130376557</v>
       </c>
       <c r="M2" t="n">
-        <v>33.68</v>
+        <v>424.9891130376558</v>
       </c>
       <c r="N2" t="n">
-        <v>433.6300000000001</v>
+        <v>841.7791130376559</v>
       </c>
       <c r="O2" t="n">
-        <v>850.4200000000001</v>
+        <v>1258.569113037656</v>
       </c>
       <c r="P2" t="n">
-        <v>1267.21</v>
+        <v>1675.359113037656</v>
       </c>
       <c r="Q2" t="n">
         <v>1684</v>
       </c>
       <c r="R2" t="n">
-        <v>1684</v>
+        <v>1513.88384708544</v>
       </c>
       <c r="S2" t="n">
-        <v>1588.193769896644</v>
+        <v>1418.077616982083</v>
       </c>
       <c r="T2" t="n">
-        <v>1399.632576231427</v>
+        <v>1229.516423316867</v>
       </c>
       <c r="U2" t="n">
-        <v>1147.893892848992</v>
+        <v>977.7777399344324</v>
       </c>
       <c r="V2" t="n">
-        <v>915.7211411653319</v>
+        <v>745.6049882507718</v>
       </c>
       <c r="W2" t="n">
-        <v>674.9398522956878</v>
+        <v>504.8236993811278</v>
       </c>
       <c r="X2" t="n">
-        <v>480.7157780929932</v>
+        <v>310.5996251784331</v>
       </c>
       <c r="Y2" t="n">
-        <v>368.2739268982392</v>
+        <v>198.1577739836791</v>
       </c>
     </row>
     <row r="3">
@@ -4376,22 +4376,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>900.0695195792149</v>
+        <v>33.68</v>
       </c>
       <c r="C3" t="n">
-        <v>698.2331546075238</v>
+        <v>33.68</v>
       </c>
       <c r="D3" t="n">
-        <v>698.2331546075238</v>
+        <v>33.68</v>
       </c>
       <c r="E3" t="n">
-        <v>698.2331546075238</v>
+        <v>33.68</v>
       </c>
       <c r="F3" t="n">
-        <v>698.2331546075238</v>
+        <v>33.68</v>
       </c>
       <c r="G3" t="n">
-        <v>369.2033203903244</v>
+        <v>33.68</v>
       </c>
       <c r="H3" t="n">
         <v>33.68</v>
@@ -4421,31 +4421,31 @@
         <v>1189.112420368536</v>
       </c>
       <c r="Q3" t="n">
-        <v>1189.112420368536</v>
+        <v>1014.284879873102</v>
       </c>
       <c r="R3" t="n">
-        <v>1040.351008962092</v>
+        <v>865.523468466658</v>
       </c>
       <c r="S3" t="n">
-        <v>973.1146453614743</v>
+        <v>440.2709432141327</v>
       </c>
       <c r="T3" t="n">
-        <v>967.7027613033796</v>
+        <v>434.8590591560379</v>
       </c>
       <c r="U3" t="n">
-        <v>967.4902766971303</v>
+        <v>101.1007571179154</v>
       </c>
       <c r="V3" t="n">
-        <v>952.8330371097362</v>
+        <v>86.44351753052129</v>
       </c>
       <c r="W3" t="n">
-        <v>920.1328927563741</v>
+        <v>53.74337317715914</v>
       </c>
       <c r="X3" t="n">
-        <v>900.0695195792149</v>
+        <v>33.68</v>
       </c>
       <c r="Y3" t="n">
-        <v>900.0695195792149</v>
+        <v>33.68</v>
       </c>
     </row>
     <row r="4">
@@ -4455,31 +4455,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>145.4373376662921</v>
+        <v>629.6886313468881</v>
       </c>
       <c r="C4" t="n">
-        <v>271.4393434847279</v>
+        <v>755.6906371653239</v>
       </c>
       <c r="D4" t="n">
-        <v>384.758487609728</v>
+        <v>869.009781290324</v>
       </c>
       <c r="E4" t="n">
-        <v>502.5873918211411</v>
+        <v>986.838685501737</v>
       </c>
       <c r="F4" t="n">
-        <v>626.9483644130765</v>
+        <v>1111.199658093672</v>
       </c>
       <c r="G4" t="n">
-        <v>780.3549302999618</v>
+        <v>1264.606223980558</v>
       </c>
       <c r="H4" t="n">
-        <v>949.8715154593593</v>
+        <v>1434.122809139956</v>
       </c>
       <c r="I4" t="n">
-        <v>1171.004394395442</v>
+        <v>1434.122809139956</v>
       </c>
       <c r="J4" t="n">
-        <v>1532.088135047894</v>
+        <v>1434.122809139956</v>
       </c>
       <c r="K4" t="n">
         <v>1544.487243076824</v>
@@ -4506,25 +4506,25 @@
         <v>33.68</v>
       </c>
       <c r="S4" t="n">
-        <v>33.68</v>
+        <v>70.93025509417312</v>
       </c>
       <c r="T4" t="n">
-        <v>33.68</v>
+        <v>168.0791097704565</v>
       </c>
       <c r="U4" t="n">
-        <v>33.68</v>
+        <v>168.0791097704565</v>
       </c>
       <c r="V4" t="n">
-        <v>33.68</v>
+        <v>366.9005026564024</v>
       </c>
       <c r="W4" t="n">
-        <v>33.68</v>
+        <v>366.9005026564024</v>
       </c>
       <c r="X4" t="n">
-        <v>33.68</v>
+        <v>517.9312936805959</v>
       </c>
       <c r="Y4" t="n">
-        <v>33.68</v>
+        <v>517.9312936805959</v>
       </c>
     </row>
     <row r="5">
@@ -4567,16 +4567,16 @@
         <v>424.9891130376557</v>
       </c>
       <c r="M5" t="n">
-        <v>433.6300000000001</v>
+        <v>841.7791130376559</v>
       </c>
       <c r="N5" t="n">
-        <v>433.6300000000001</v>
+        <v>1258.569113037656</v>
       </c>
       <c r="O5" t="n">
-        <v>850.4200000000001</v>
+        <v>1675.359113037656</v>
       </c>
       <c r="P5" t="n">
-        <v>1267.21</v>
+        <v>1675.359113037656</v>
       </c>
       <c r="Q5" t="n">
         <v>1684</v>
@@ -4613,16 +4613,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>385.1322089875785</v>
+        <v>900.0695195792149</v>
       </c>
       <c r="C6" t="n">
-        <v>385.1322089875785</v>
+        <v>900.0695195792149</v>
       </c>
       <c r="D6" t="n">
-        <v>33.68</v>
+        <v>722.8803429896864</v>
       </c>
       <c r="E6" t="n">
-        <v>33.68</v>
+        <v>376.7469114524009</v>
       </c>
       <c r="F6" t="n">
         <v>33.68</v>
@@ -4658,31 +4658,31 @@
         <v>1189.112420368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1014.284879873102</v>
+        <v>1189.112420368536</v>
       </c>
       <c r="R6" t="n">
-        <v>589.0323546205764</v>
+        <v>1040.351008962092</v>
       </c>
       <c r="S6" t="n">
-        <v>521.7959910199589</v>
+        <v>973.1146453614743</v>
       </c>
       <c r="T6" t="n">
-        <v>516.3841069618642</v>
+        <v>967.7027613033796</v>
       </c>
       <c r="U6" t="n">
-        <v>516.1716223556149</v>
+        <v>967.4902766971303</v>
       </c>
       <c r="V6" t="n">
-        <v>437.8957265180997</v>
+        <v>952.8330371097362</v>
       </c>
       <c r="W6" t="n">
-        <v>405.1955821647376</v>
+        <v>920.1328927563741</v>
       </c>
       <c r="X6" t="n">
-        <v>385.1322089875785</v>
+        <v>900.0695195792149</v>
       </c>
       <c r="Y6" t="n">
-        <v>385.1322089875785</v>
+        <v>900.0695195792149</v>
       </c>
     </row>
     <row r="7">
@@ -4692,19 +4692,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1153.837778981343</v>
+        <v>643.2811589396091</v>
       </c>
       <c r="C7" t="n">
-        <v>1153.837778981343</v>
+        <v>769.2831647580449</v>
       </c>
       <c r="D7" t="n">
-        <v>1153.837778981343</v>
+        <v>882.602308883045</v>
       </c>
       <c r="E7" t="n">
-        <v>1153.837778981343</v>
+        <v>1000.431213094458</v>
       </c>
       <c r="F7" t="n">
-        <v>1153.837778981343</v>
+        <v>1000.431213094458</v>
       </c>
       <c r="G7" t="n">
         <v>1153.837778981343</v>
@@ -4743,25 +4743,25 @@
         <v>33.68</v>
       </c>
       <c r="S7" t="n">
-        <v>70.93025509417312</v>
+        <v>33.68</v>
       </c>
       <c r="T7" t="n">
-        <v>259.005934252978</v>
+        <v>33.68</v>
       </c>
       <c r="U7" t="n">
-        <v>505.5571268912646</v>
+        <v>33.68</v>
       </c>
       <c r="V7" t="n">
-        <v>704.3785197772106</v>
+        <v>208.9501489767059</v>
       </c>
       <c r="W7" t="n">
-        <v>876.269438036888</v>
+        <v>380.8410672363833</v>
       </c>
       <c r="X7" t="n">
-        <v>1027.300229061082</v>
+        <v>531.8718582605768</v>
       </c>
       <c r="Y7" t="n">
-        <v>1042.080441315051</v>
+        <v>643.2811589396091</v>
       </c>
     </row>
     <row r="8">
@@ -4801,19 +4801,19 @@
         <v>424.9891130376557</v>
       </c>
       <c r="L8" t="n">
-        <v>424.9891130376557</v>
+        <v>841.7791130376557</v>
       </c>
       <c r="M8" t="n">
-        <v>433.6300000000001</v>
+        <v>1258.569113037656</v>
       </c>
       <c r="N8" t="n">
-        <v>850.4200000000001</v>
+        <v>1675.359113037656</v>
       </c>
       <c r="O8" t="n">
-        <v>1267.21</v>
+        <v>1675.359113037656</v>
       </c>
       <c r="P8" t="n">
-        <v>1267.21</v>
+        <v>1675.359113037656</v>
       </c>
       <c r="Q8" t="n">
         <v>1684</v>
@@ -4831,16 +4831,16 @@
         <v>1147.893892848992</v>
       </c>
       <c r="V8" t="n">
-        <v>745.6049882507718</v>
+        <v>915.7211411653319</v>
       </c>
       <c r="W8" t="n">
-        <v>504.8236993811278</v>
+        <v>674.9398522956878</v>
       </c>
       <c r="X8" t="n">
-        <v>310.5996251784331</v>
+        <v>480.7157780929932</v>
       </c>
       <c r="Y8" t="n">
-        <v>198.1577739836791</v>
+        <v>368.2739268982392</v>
       </c>
     </row>
     <row r="9">
@@ -4895,25 +4895,25 @@
         <v>1189.112420368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1014.284879873102</v>
+        <v>1189.112420368536</v>
       </c>
       <c r="R9" t="n">
-        <v>865.523468466658</v>
+        <v>763.8598951160103</v>
       </c>
       <c r="S9" t="n">
-        <v>499.2775066814225</v>
+        <v>696.6235315153929</v>
       </c>
       <c r="T9" t="n">
-        <v>493.8656226233277</v>
+        <v>691.2116474572981</v>
       </c>
       <c r="U9" t="n">
-        <v>493.6531380170785</v>
+        <v>690.9991628510488</v>
       </c>
       <c r="V9" t="n">
-        <v>478.9958984296844</v>
+        <v>676.3419232636547</v>
       </c>
       <c r="W9" t="n">
-        <v>53.74337317715914</v>
+        <v>457.7837772175632</v>
       </c>
       <c r="X9" t="n">
         <v>33.68</v>
@@ -4929,31 +4929,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>544.6773884426758</v>
+        <v>408.5557524108052</v>
       </c>
       <c r="C10" t="n">
-        <v>544.6773884426758</v>
+        <v>534.557758229241</v>
       </c>
       <c r="D10" t="n">
-        <v>657.9965325676759</v>
+        <v>647.8769023542411</v>
       </c>
       <c r="E10" t="n">
-        <v>775.8254367790889</v>
+        <v>765.7058065656541</v>
       </c>
       <c r="F10" t="n">
-        <v>900.1864093710244</v>
+        <v>890.0667791575896</v>
       </c>
       <c r="G10" t="n">
-        <v>1053.59297525791</v>
+        <v>1043.473345044475</v>
       </c>
       <c r="H10" t="n">
-        <v>1223.109560417307</v>
+        <v>1212.989930203873</v>
       </c>
       <c r="I10" t="n">
-        <v>1444.24243935339</v>
+        <v>1434.122809139956</v>
       </c>
       <c r="J10" t="n">
-        <v>1544.487243076824</v>
+        <v>1434.122809139956</v>
       </c>
       <c r="K10" t="n">
         <v>1544.487243076824</v>
@@ -4980,25 +4980,25 @@
         <v>33.68</v>
       </c>
       <c r="S10" t="n">
-        <v>33.68</v>
+        <v>34.35832304128732</v>
       </c>
       <c r="T10" t="n">
-        <v>221.7556791588049</v>
+        <v>34.35832304128732</v>
       </c>
       <c r="U10" t="n">
-        <v>221.7556791588049</v>
+        <v>34.35832304128732</v>
       </c>
       <c r="V10" t="n">
-        <v>221.7556791588049</v>
+        <v>34.35832304128732</v>
       </c>
       <c r="W10" t="n">
-        <v>393.6465974184823</v>
+        <v>34.35832304128732</v>
       </c>
       <c r="X10" t="n">
-        <v>544.6773884426758</v>
+        <v>185.3891140654808</v>
       </c>
       <c r="Y10" t="n">
-        <v>544.6773884426758</v>
+        <v>296.7984147445131</v>
       </c>
     </row>
     <row r="11">
@@ -5035,7 +5035,7 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K11" t="n">
-        <v>989.4391130376558</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L11" t="n">
         <v>989.4391130376558</v>
@@ -5087,19 +5087,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>55.93203277325181</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C12" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D12" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="E12" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="F12" t="n">
-        <v>44.72</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="G12" t="n">
         <v>44.72</v>
@@ -5135,28 +5135,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R12" t="n">
-        <v>647.3506049216877</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S12" t="n">
-        <v>466.2983195781991</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T12" t="n">
-        <v>410.3813850150538</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U12" t="n">
-        <v>359.6638499037541</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V12" t="n">
-        <v>294.5015598113094</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W12" t="n">
-        <v>211.2963649528968</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X12" t="n">
-        <v>140.7279412706871</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y12" t="n">
-        <v>90.8376455473191</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="13">
@@ -5245,16 +5245,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C14" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D14" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E14" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F14" t="n">
         <v>157.615990899539</v>
@@ -5269,22 +5269,22 @@
         <v>44.72</v>
       </c>
       <c r="J14" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K14" t="n">
-        <v>989.4391130376558</v>
+        <v>44.72</v>
       </c>
       <c r="L14" t="n">
-        <v>989.4391130376558</v>
+        <v>44.72</v>
       </c>
       <c r="M14" t="n">
-        <v>1500.287941766591</v>
+        <v>555.568828728935</v>
       </c>
       <c r="N14" t="n">
-        <v>1797.400904947332</v>
+        <v>1108.978828728935</v>
       </c>
       <c r="O14" t="n">
-        <v>1797.400904947332</v>
+        <v>1662.388828728935</v>
       </c>
       <c r="P14" t="n">
         <v>1797.400904947332</v>
@@ -5296,25 +5296,25 @@
         <v>2236</v>
       </c>
       <c r="S14" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T14" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U14" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V14" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W14" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X14" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y14" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="15">
@@ -5333,13 +5333,13 @@
         <v>461.5662247731743</v>
       </c>
       <c r="E15" t="n">
-        <v>387.7869114524009</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="F15" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="G15" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="H15" t="n">
         <v>44.72</v>
@@ -5506,10 +5506,10 @@
         <v>44.72</v>
       </c>
       <c r="J17" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K17" t="n">
-        <v>733.1420762183976</v>
+        <v>598.13</v>
       </c>
       <c r="L17" t="n">
         <v>733.1420762183976</v>
@@ -5530,7 +5530,7 @@
         <v>2236</v>
       </c>
       <c r="R17" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S17" t="n">
         <v>2085.68327354774</v>
@@ -5561,16 +5561,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>472.7782575464261</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C18" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="D18" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="E18" t="n">
-        <v>387.7869114524009</v>
+        <v>44.72</v>
       </c>
       <c r="F18" t="n">
         <v>44.72</v>
@@ -5609,28 +5609,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R18" t="n">
-        <v>1000.885958457041</v>
+        <v>647.3506049216877</v>
       </c>
       <c r="S18" t="n">
-        <v>883.1445443513733</v>
+        <v>529.6091908160197</v>
       </c>
       <c r="T18" t="n">
-        <v>827.2276097882281</v>
+        <v>473.6922562528744</v>
       </c>
       <c r="U18" t="n">
-        <v>776.5100746769283</v>
+        <v>422.9747211415747</v>
       </c>
       <c r="V18" t="n">
-        <v>711.3477845844836</v>
+        <v>357.8124310491301</v>
       </c>
       <c r="W18" t="n">
-        <v>628.142589726071</v>
+        <v>274.6072361907174</v>
       </c>
       <c r="X18" t="n">
-        <v>557.5741660438614</v>
+        <v>204.0388125085078</v>
       </c>
       <c r="Y18" t="n">
-        <v>507.6838703204934</v>
+        <v>154.1485167851397</v>
       </c>
     </row>
     <row r="19">
@@ -5743,22 +5743,22 @@
         <v>44.72</v>
       </c>
       <c r="J20" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K20" t="n">
-        <v>436.0291130376557</v>
+        <v>598.13</v>
       </c>
       <c r="L20" t="n">
-        <v>436.0291130376557</v>
+        <v>1151.54</v>
       </c>
       <c r="M20" t="n">
-        <v>946.8779417665908</v>
+        <v>1662.388828728935</v>
       </c>
       <c r="N20" t="n">
-        <v>1243.990904947333</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O20" t="n">
-        <v>1243.990904947333</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P20" t="n">
         <v>1797.400904947332</v>
@@ -5767,7 +5767,7 @@
         <v>2236</v>
       </c>
       <c r="R20" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S20" t="n">
         <v>2085.68327354774</v>
@@ -5798,10 +5798,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>119.2429040110725</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C21" t="n">
-        <v>108.0308712378206</v>
+        <v>44.72</v>
       </c>
       <c r="D21" t="n">
         <v>44.72</v>
@@ -5849,25 +5849,25 @@
         <v>647.3506049216877</v>
       </c>
       <c r="S21" t="n">
-        <v>529.6091908160197</v>
+        <v>466.2983195781991</v>
       </c>
       <c r="T21" t="n">
-        <v>473.6922562528744</v>
+        <v>410.3813850150538</v>
       </c>
       <c r="U21" t="n">
-        <v>422.9747211415747</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V21" t="n">
-        <v>357.8124310491301</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W21" t="n">
-        <v>274.6072361907174</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X21" t="n">
-        <v>204.0388125085078</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y21" t="n">
-        <v>154.1485167851397</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="22">
@@ -5956,22 +5956,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C23" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D23" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E23" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F23" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G23" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H23" t="n">
         <v>44.72</v>
@@ -5983,49 +5983,49 @@
         <v>44.72</v>
       </c>
       <c r="K23" t="n">
-        <v>598.13</v>
+        <v>44.72</v>
       </c>
       <c r="L23" t="n">
-        <v>1151.54</v>
+        <v>44.72</v>
       </c>
       <c r="M23" t="n">
-        <v>1662.388828728935</v>
+        <v>555.568828728935</v>
       </c>
       <c r="N23" t="n">
-        <v>2215.798828728935</v>
+        <v>1108.978828728935</v>
       </c>
       <c r="O23" t="n">
-        <v>2215.798828728935</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="P23" t="n">
-        <v>2215.798828728935</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q23" t="n">
         <v>2236</v>
       </c>
       <c r="R23" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S23" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T23" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U23" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V23" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W23" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X23" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y23" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="24">
@@ -6035,22 +6035,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>409.4673863086053</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C24" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D24" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="E24" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="F24" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="G24" t="n">
-        <v>44.72</v>
+        <v>132.5363905559749</v>
       </c>
       <c r="H24" t="n">
         <v>44.72</v>
@@ -6083,28 +6083,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R24" t="n">
-        <v>937.5750872192206</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S24" t="n">
-        <v>819.8336731135525</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T24" t="n">
-        <v>763.9167385504073</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U24" t="n">
-        <v>713.1992034391076</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V24" t="n">
-        <v>648.0369133466629</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W24" t="n">
-        <v>564.8317184882503</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X24" t="n">
-        <v>494.2632948060406</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y24" t="n">
-        <v>444.3729990826726</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="25">
@@ -6193,76 +6193,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>670.2544188625992</v>
+        <v>676.8041245336038</v>
       </c>
       <c r="C26" t="n">
-        <v>530.3811075060397</v>
+        <v>536.9308131770443</v>
       </c>
       <c r="D26" t="n">
-        <v>430.0385259506359</v>
+        <v>436.5882316216405</v>
       </c>
       <c r="E26" t="n">
-        <v>335.7321728123847</v>
+        <v>342.2818784833894</v>
       </c>
       <c r="F26" t="n">
-        <v>247.4438696874237</v>
+        <v>247.4438696874178</v>
       </c>
       <c r="G26" t="n">
-        <v>153.7495542459932</v>
+        <v>153.7495542459873</v>
       </c>
       <c r="H26" t="n">
-        <v>55.76000000000587</v>
+        <v>55.76</v>
       </c>
       <c r="I26" t="n">
-        <v>55.76000000000587</v>
+        <v>55.76</v>
       </c>
       <c r="J26" t="n">
-        <v>447.0691130376616</v>
+        <v>447.0691130376557</v>
       </c>
       <c r="K26" t="n">
-        <v>1137.099113037734</v>
+        <v>1137.099113037656</v>
       </c>
       <c r="L26" t="n">
-        <v>1137.099113037734</v>
+        <v>1137.099113037656</v>
       </c>
       <c r="M26" t="n">
-        <v>1647.947941766669</v>
+        <v>1647.947941766591</v>
       </c>
       <c r="N26" t="n">
-        <v>1647.947941766669</v>
+        <v>2261.168261541354</v>
       </c>
       <c r="O26" t="n">
-        <v>2337.977941766742</v>
+        <v>2788</v>
       </c>
       <c r="P26" t="n">
-        <v>2349.400904947626</v>
+        <v>2788</v>
       </c>
       <c r="Q26" t="n">
-        <v>2788.000000000294</v>
+        <v>2788</v>
       </c>
       <c r="R26" t="n">
-        <v>2788.000000000294</v>
+        <v>2788</v>
       </c>
       <c r="S26" t="n">
-        <v>2602.294779997947</v>
+        <v>2602.294779997654</v>
       </c>
       <c r="T26" t="n">
-        <v>2323.834596433741</v>
+        <v>2323.834596433448</v>
       </c>
       <c r="U26" t="n">
-        <v>1982.196923152316</v>
+        <v>1982.196923152023</v>
       </c>
       <c r="V26" t="n">
-        <v>1660.125181569666</v>
+        <v>1660.125181569372</v>
       </c>
       <c r="W26" t="n">
-        <v>1329.444902801032</v>
+        <v>1329.444902800738</v>
       </c>
       <c r="X26" t="n">
-        <v>1045.321838699348</v>
+        <v>1051.871544370352</v>
       </c>
       <c r="Y26" t="n">
-        <v>842.9809976056038</v>
+        <v>849.5307032766084</v>
       </c>
     </row>
     <row r="27">
@@ -6272,76 +6272,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>240.8646080449149</v>
+        <v>240.8646080449089</v>
       </c>
       <c r="C27" t="n">
-        <v>190.2586358777236</v>
+        <v>190.2586358777178</v>
       </c>
       <c r="D27" t="n">
-        <v>152.9478410315594</v>
+        <v>152.9478410315535</v>
       </c>
       <c r="E27" t="n">
-        <v>120.955823635688</v>
+        <v>120.9558236356822</v>
       </c>
       <c r="F27" t="n">
-        <v>92.03032632470131</v>
+        <v>92.03032632469542</v>
       </c>
       <c r="G27" t="n">
-        <v>77.14190624891611</v>
+        <v>77.14190624891023</v>
       </c>
       <c r="H27" t="n">
-        <v>55.76000000000587</v>
+        <v>55.76</v>
       </c>
       <c r="I27" t="n">
-        <v>55.76000000000587</v>
+        <v>55.76</v>
       </c>
       <c r="J27" t="n">
-        <v>179.7165201753048</v>
+        <v>179.7165201752989</v>
       </c>
       <c r="K27" t="n">
-        <v>480.5011413136259</v>
+        <v>368.9093362696823</v>
       </c>
       <c r="L27" t="n">
-        <v>751.851602908826</v>
+        <v>640.2597978648824</v>
       </c>
       <c r="M27" t="n">
-        <v>837.9321446516852</v>
+        <v>726.3403396077417</v>
       </c>
       <c r="N27" t="n">
-        <v>971.2124292592536</v>
+        <v>859.62062421531</v>
       </c>
       <c r="O27" t="n">
-        <v>1210.254880942972</v>
+        <v>1098.663075899029</v>
       </c>
       <c r="P27" t="n">
-        <v>1322.784225412479</v>
+        <v>1211.192420368536</v>
       </c>
       <c r="Q27" t="n">
-        <v>1322.784225412479</v>
+        <v>1322.784225412473</v>
       </c>
       <c r="R27" t="n">
-        <v>1084.123824107045</v>
+        <v>1084.12382410704</v>
       </c>
       <c r="S27" t="n">
-        <v>926.988470607438</v>
+        <v>926.9884706074321</v>
       </c>
       <c r="T27" t="n">
-        <v>831.6775966503533</v>
+        <v>831.6775966503474</v>
       </c>
       <c r="U27" t="n">
-        <v>741.5661221451142</v>
+        <v>741.5661221451082</v>
       </c>
       <c r="V27" t="n">
-        <v>637.0098926587301</v>
+        <v>637.0098926587242</v>
       </c>
       <c r="W27" t="n">
-        <v>514.410758406378</v>
+        <v>514.4107584063721</v>
       </c>
       <c r="X27" t="n">
-        <v>404.448395330229</v>
+        <v>404.4483953302231</v>
       </c>
       <c r="Y27" t="n">
-        <v>315.1641602129216</v>
+        <v>315.1641602129156</v>
       </c>
     </row>
     <row r="28">
@@ -6351,76 +6351,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>618.5266123122387</v>
+        <v>618.5266123122328</v>
       </c>
       <c r="C28" t="n">
-        <v>656.4186181306745</v>
+        <v>656.4186181306686</v>
       </c>
       <c r="D28" t="n">
-        <v>681.6277622556746</v>
+        <v>681.6277622556687</v>
       </c>
       <c r="E28" t="n">
-        <v>711.3466664670876</v>
+        <v>711.3466664670817</v>
       </c>
       <c r="F28" t="n">
-        <v>747.5976390590231</v>
+        <v>747.5976390590172</v>
       </c>
       <c r="G28" t="n">
-        <v>812.8942049459083</v>
+        <v>812.8942049459024</v>
       </c>
       <c r="H28" t="n">
-        <v>894.3007901053059</v>
+        <v>894.3007901052999</v>
       </c>
       <c r="I28" t="n">
-        <v>1027.323669041389</v>
+        <v>1027.323669041383</v>
       </c>
       <c r="J28" t="n">
-        <v>1300.29740969384</v>
+        <v>1300.297409693834</v>
       </c>
       <c r="K28" t="n">
-        <v>1322.551843630708</v>
+        <v>1322.551843630702</v>
       </c>
       <c r="L28" t="n">
-        <v>1322.551843630708</v>
+        <v>1322.551843630702</v>
       </c>
       <c r="M28" t="n">
-        <v>1322.551843630708</v>
+        <v>1322.551843630702</v>
       </c>
       <c r="N28" t="n">
-        <v>1322.551843630708</v>
+        <v>1322.551843630702</v>
       </c>
       <c r="O28" t="n">
-        <v>1274.840092661649</v>
+        <v>1274.840092661643</v>
       </c>
       <c r="P28" t="n">
-        <v>894.5896913199545</v>
+        <v>894.5896913199485</v>
       </c>
       <c r="Q28" t="n">
-        <v>475.5601292738959</v>
+        <v>475.56012927389</v>
       </c>
       <c r="R28" t="n">
-        <v>55.76000000000587</v>
+        <v>55.76</v>
       </c>
       <c r="S28" t="n">
-        <v>55.76000000000587</v>
+        <v>55.76</v>
       </c>
       <c r="T28" t="n">
-        <v>155.7256791588107</v>
+        <v>155.7256791588049</v>
       </c>
       <c r="U28" t="n">
-        <v>314.1668717970974</v>
+        <v>314.1668717970915</v>
       </c>
       <c r="V28" t="n">
-        <v>424.8782646830434</v>
+        <v>424.8782646830375</v>
       </c>
       <c r="W28" t="n">
-        <v>508.6591829427208</v>
+        <v>508.6591829427149</v>
       </c>
       <c r="X28" t="n">
-        <v>571.5799739669143</v>
+        <v>571.5799739669084</v>
       </c>
       <c r="Y28" t="n">
-        <v>594.8792746459466</v>
+        <v>594.8792746459407</v>
       </c>
     </row>
     <row r="29">
@@ -6430,76 +6430,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>670.2544188625164</v>
+        <v>676.8041245333126</v>
       </c>
       <c r="C29" t="n">
-        <v>530.3811075059569</v>
+        <v>536.9308131767531</v>
       </c>
       <c r="D29" t="n">
-        <v>430.0385259505531</v>
+        <v>436.5882316213493</v>
       </c>
       <c r="E29" t="n">
-        <v>335.7321728123019</v>
+        <v>342.2818784830981</v>
       </c>
       <c r="F29" t="n">
-        <v>247.4438696874237</v>
+        <v>247.4438696871265</v>
       </c>
       <c r="G29" t="n">
-        <v>153.7495542459932</v>
+        <v>153.749554245696</v>
       </c>
       <c r="H29" t="n">
-        <v>55.76000000000587</v>
+        <v>55.75999999970873</v>
       </c>
       <c r="I29" t="n">
-        <v>55.76000000000587</v>
+        <v>55.76</v>
       </c>
       <c r="J29" t="n">
-        <v>447.0691130376616</v>
+        <v>55.76</v>
       </c>
       <c r="K29" t="n">
-        <v>447.0691130376616</v>
+        <v>745.79</v>
       </c>
       <c r="L29" t="n">
-        <v>447.0691130376616</v>
+        <v>1225.331756443634</v>
       </c>
       <c r="M29" t="n">
-        <v>957.9179417665966</v>
+        <v>1736.180585172569</v>
       </c>
       <c r="N29" t="n">
-        <v>1571.13826154136</v>
+        <v>2349.400904947332</v>
       </c>
       <c r="O29" t="n">
-        <v>2261.168261541433</v>
+        <v>2349.400904947332</v>
       </c>
       <c r="P29" t="n">
-        <v>2349.400904947626</v>
+        <v>2349.400904947332</v>
       </c>
       <c r="Q29" t="n">
-        <v>2788.000000000294</v>
+        <v>2788</v>
       </c>
       <c r="R29" t="n">
-        <v>2788.000000000211</v>
+        <v>2788</v>
       </c>
       <c r="S29" t="n">
-        <v>2602.294779997865</v>
+        <v>2608.844485668661</v>
       </c>
       <c r="T29" t="n">
-        <v>2323.834596433659</v>
+        <v>2330.384302104455</v>
       </c>
       <c r="U29" t="n">
-        <v>1982.196923152234</v>
+        <v>1988.74662882303</v>
       </c>
       <c r="V29" t="n">
-        <v>1660.125181569583</v>
+        <v>1666.67488724038</v>
       </c>
       <c r="W29" t="n">
-        <v>1329.444902800949</v>
+        <v>1335.994608471746</v>
       </c>
       <c r="X29" t="n">
-        <v>1045.321838699265</v>
+        <v>1051.871544370061</v>
       </c>
       <c r="Y29" t="n">
-        <v>842.980997605521</v>
+        <v>849.5307032763171</v>
       </c>
     </row>
     <row r="30">
@@ -6509,76 +6509,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>240.8646080449149</v>
+        <v>240.8646080449089</v>
       </c>
       <c r="C30" t="n">
-        <v>190.2586358777236</v>
+        <v>190.2586358777178</v>
       </c>
       <c r="D30" t="n">
-        <v>152.9478410315594</v>
+        <v>152.9478410315535</v>
       </c>
       <c r="E30" t="n">
-        <v>120.955823635688</v>
+        <v>120.9558236356822</v>
       </c>
       <c r="F30" t="n">
-        <v>92.03032632470131</v>
+        <v>92.03032632469542</v>
       </c>
       <c r="G30" t="n">
-        <v>77.14190624891611</v>
+        <v>77.14190624891023</v>
       </c>
       <c r="H30" t="n">
-        <v>55.76000000000587</v>
+        <v>55.76</v>
       </c>
       <c r="I30" t="n">
-        <v>55.76000000000587</v>
+        <v>55.76</v>
       </c>
       <c r="J30" t="n">
-        <v>179.7165201753048</v>
+        <v>179.7165201752989</v>
       </c>
       <c r="K30" t="n">
-        <v>368.9093362696882</v>
+        <v>368.9093362696823</v>
       </c>
       <c r="L30" t="n">
-        <v>640.2597978648882</v>
+        <v>640.2597978648824</v>
       </c>
       <c r="M30" t="n">
-        <v>726.3403396077475</v>
+        <v>726.3403396077417</v>
       </c>
       <c r="N30" t="n">
-        <v>859.6206242153158</v>
+        <v>859.62062421531</v>
       </c>
       <c r="O30" t="n">
-        <v>1098.663075899035</v>
+        <v>1098.663075899029</v>
       </c>
       <c r="P30" t="n">
-        <v>1211.192420368541</v>
+        <v>1211.192420368536</v>
       </c>
       <c r="Q30" t="n">
-        <v>1322.784225412479</v>
+        <v>1322.784225412473</v>
       </c>
       <c r="R30" t="n">
-        <v>1084.123824107045</v>
+        <v>1084.12382410704</v>
       </c>
       <c r="S30" t="n">
-        <v>926.988470607438</v>
+        <v>926.9884706074321</v>
       </c>
       <c r="T30" t="n">
-        <v>831.6775966503533</v>
+        <v>831.6775966503474</v>
       </c>
       <c r="U30" t="n">
-        <v>741.5661221451142</v>
+        <v>741.5661221451082</v>
       </c>
       <c r="V30" t="n">
-        <v>637.0098926587301</v>
+        <v>637.0098926587242</v>
       </c>
       <c r="W30" t="n">
-        <v>514.410758406378</v>
+        <v>514.4107584063721</v>
       </c>
       <c r="X30" t="n">
-        <v>404.448395330229</v>
+        <v>404.4483953302231</v>
       </c>
       <c r="Y30" t="n">
-        <v>315.1641602129216</v>
+        <v>315.1641602129156</v>
       </c>
     </row>
     <row r="31">
@@ -6588,76 +6588,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>618.5266123122387</v>
+        <v>618.5266123122328</v>
       </c>
       <c r="C31" t="n">
-        <v>656.4186181306745</v>
+        <v>656.4186181306686</v>
       </c>
       <c r="D31" t="n">
-        <v>681.6277622556746</v>
+        <v>681.6277622556687</v>
       </c>
       <c r="E31" t="n">
-        <v>711.3466664670876</v>
+        <v>711.3466664670817</v>
       </c>
       <c r="F31" t="n">
-        <v>747.5976390590231</v>
+        <v>747.5976390590172</v>
       </c>
       <c r="G31" t="n">
-        <v>812.8942049459083</v>
+        <v>812.8942049459024</v>
       </c>
       <c r="H31" t="n">
-        <v>894.3007901053059</v>
+        <v>894.3007901052999</v>
       </c>
       <c r="I31" t="n">
-        <v>1027.323669041389</v>
+        <v>1027.323669041383</v>
       </c>
       <c r="J31" t="n">
-        <v>1300.29740969384</v>
+        <v>1300.297409693834</v>
       </c>
       <c r="K31" t="n">
-        <v>1322.551843630708</v>
+        <v>1322.551843630702</v>
       </c>
       <c r="L31" t="n">
-        <v>1322.551843630708</v>
+        <v>1322.551843630702</v>
       </c>
       <c r="M31" t="n">
-        <v>1110.80274120389</v>
+        <v>1322.551843630702</v>
       </c>
       <c r="N31" t="n">
-        <v>847.9895338587539</v>
+        <v>1187.813260437263</v>
       </c>
       <c r="O31" t="n">
-        <v>515.2162368092438</v>
+        <v>855.039963387753</v>
       </c>
       <c r="P31" t="n">
-        <v>515.2162368092438</v>
+        <v>474.7895620460586</v>
       </c>
       <c r="Q31" t="n">
-        <v>515.2162368092438</v>
+        <v>55.76</v>
       </c>
       <c r="R31" t="n">
-        <v>95.41610753535383</v>
+        <v>55.76</v>
       </c>
       <c r="S31" t="n">
-        <v>55.76000000000587</v>
+        <v>55.76</v>
       </c>
       <c r="T31" t="n">
-        <v>155.7256791588107</v>
+        <v>155.7256791588049</v>
       </c>
       <c r="U31" t="n">
-        <v>314.1668717970974</v>
+        <v>314.1668717970915</v>
       </c>
       <c r="V31" t="n">
-        <v>424.8782646830434</v>
+        <v>424.8782646830375</v>
       </c>
       <c r="W31" t="n">
-        <v>508.6591829427208</v>
+        <v>508.6591829427149</v>
       </c>
       <c r="X31" t="n">
-        <v>571.5799739669143</v>
+        <v>571.5799739669084</v>
       </c>
       <c r="Y31" t="n">
-        <v>594.8792746459466</v>
+        <v>594.8792746459407</v>
       </c>
     </row>
     <row r="32">
@@ -6667,76 +6667,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>676.8041245336098</v>
+        <v>670.2544188623054</v>
       </c>
       <c r="C32" t="n">
-        <v>536.9308131770503</v>
+        <v>530.3811075057459</v>
       </c>
       <c r="D32" t="n">
-        <v>436.5882316216465</v>
+        <v>430.0385259503421</v>
       </c>
       <c r="E32" t="n">
-        <v>342.2818784833953</v>
+        <v>335.7321728120909</v>
       </c>
       <c r="F32" t="n">
-        <v>247.4438696874237</v>
+        <v>247.4438696874178</v>
       </c>
       <c r="G32" t="n">
-        <v>153.7495542459932</v>
+        <v>153.7495542459873</v>
       </c>
       <c r="H32" t="n">
-        <v>55.76000000000587</v>
+        <v>55.76</v>
       </c>
       <c r="I32" t="n">
-        <v>55.76000000000587</v>
+        <v>55.76</v>
       </c>
       <c r="J32" t="n">
-        <v>447.0691130376616</v>
+        <v>55.76</v>
       </c>
       <c r="K32" t="n">
-        <v>447.0691130376616</v>
+        <v>55.76</v>
       </c>
       <c r="L32" t="n">
-        <v>447.0691130376616</v>
+        <v>55.76</v>
       </c>
       <c r="M32" t="n">
-        <v>957.9179417665966</v>
+        <v>566.608828728935</v>
       </c>
       <c r="N32" t="n">
-        <v>1571.13826154136</v>
+        <v>1179.829148503698</v>
       </c>
       <c r="O32" t="n">
-        <v>1659.370904947554</v>
+        <v>1869.859148503698</v>
       </c>
       <c r="P32" t="n">
-        <v>2349.400904947626</v>
+        <v>2559.889148503698</v>
       </c>
       <c r="Q32" t="n">
-        <v>2788.000000000294</v>
+        <v>2788</v>
       </c>
       <c r="R32" t="n">
-        <v>2788.000000000294</v>
+        <v>2788</v>
       </c>
       <c r="S32" t="n">
-        <v>2608.844485668958</v>
+        <v>2602.294779997654</v>
       </c>
       <c r="T32" t="n">
-        <v>2330.384302104752</v>
+        <v>2323.834596433448</v>
       </c>
       <c r="U32" t="n">
-        <v>1988.746628823327</v>
+        <v>1982.196923152023</v>
       </c>
       <c r="V32" t="n">
-        <v>1666.674887240677</v>
+        <v>1660.125181569372</v>
       </c>
       <c r="W32" t="n">
-        <v>1335.994608472043</v>
+        <v>1329.444902800738</v>
       </c>
       <c r="X32" t="n">
-        <v>1051.871544370358</v>
+        <v>1045.321838699054</v>
       </c>
       <c r="Y32" t="n">
-        <v>849.5307032766143</v>
+        <v>842.98099760531</v>
       </c>
     </row>
     <row r="33">
@@ -6746,76 +6746,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>240.8646080449149</v>
+        <v>240.8646080449089</v>
       </c>
       <c r="C33" t="n">
-        <v>190.2586358777236</v>
+        <v>190.2586358777178</v>
       </c>
       <c r="D33" t="n">
-        <v>152.9478410315594</v>
+        <v>152.9478410315535</v>
       </c>
       <c r="E33" t="n">
-        <v>120.955823635688</v>
+        <v>120.9558236356822</v>
       </c>
       <c r="F33" t="n">
-        <v>92.03032632470131</v>
+        <v>92.03032632469542</v>
       </c>
       <c r="G33" t="n">
-        <v>77.14190624891611</v>
+        <v>77.14190624891023</v>
       </c>
       <c r="H33" t="n">
-        <v>55.76000000000587</v>
+        <v>55.76</v>
       </c>
       <c r="I33" t="n">
-        <v>55.76000000000587</v>
+        <v>148.6948779675649</v>
       </c>
       <c r="J33" t="n">
-        <v>179.7165201753048</v>
+        <v>272.6513981428639</v>
       </c>
       <c r="K33" t="n">
-        <v>368.9093362696882</v>
+        <v>461.8442142372472</v>
       </c>
       <c r="L33" t="n">
-        <v>640.2597978648882</v>
+        <v>733.1946758324473</v>
       </c>
       <c r="M33" t="n">
-        <v>726.3403396077475</v>
+        <v>819.2752175753066</v>
       </c>
       <c r="N33" t="n">
-        <v>859.6206242153158</v>
+        <v>952.5555021828749</v>
       </c>
       <c r="O33" t="n">
-        <v>1098.663075899035</v>
+        <v>1191.597953866594</v>
       </c>
       <c r="P33" t="n">
-        <v>1211.192420368541</v>
+        <v>1304.1272983361</v>
       </c>
       <c r="Q33" t="n">
-        <v>1322.784225412479</v>
+        <v>1322.784225412473</v>
       </c>
       <c r="R33" t="n">
-        <v>1084.123824107045</v>
+        <v>1084.12382410704</v>
       </c>
       <c r="S33" t="n">
-        <v>926.988470607438</v>
+        <v>926.9884706074321</v>
       </c>
       <c r="T33" t="n">
-        <v>831.6775966503533</v>
+        <v>831.6775966503474</v>
       </c>
       <c r="U33" t="n">
-        <v>741.5661221451142</v>
+        <v>741.5661221451082</v>
       </c>
       <c r="V33" t="n">
-        <v>637.0098926587301</v>
+        <v>637.0098926587242</v>
       </c>
       <c r="W33" t="n">
-        <v>514.410758406378</v>
+        <v>514.4107584063721</v>
       </c>
       <c r="X33" t="n">
-        <v>404.448395330229</v>
+        <v>404.4483953302231</v>
       </c>
       <c r="Y33" t="n">
-        <v>315.1641602129216</v>
+        <v>315.1641602129156</v>
       </c>
     </row>
     <row r="34">
@@ -6825,76 +6825,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>618.5266123122387</v>
+        <v>618.5266123122328</v>
       </c>
       <c r="C34" t="n">
-        <v>656.4186181306745</v>
+        <v>656.4186181306686</v>
       </c>
       <c r="D34" t="n">
-        <v>681.6277622556746</v>
+        <v>681.6277622556687</v>
       </c>
       <c r="E34" t="n">
-        <v>711.3466664670876</v>
+        <v>711.3466664670817</v>
       </c>
       <c r="F34" t="n">
-        <v>747.5976390590231</v>
+        <v>747.5976390590172</v>
       </c>
       <c r="G34" t="n">
-        <v>812.8942049459083</v>
+        <v>812.8942049459024</v>
       </c>
       <c r="H34" t="n">
-        <v>894.3007901053059</v>
+        <v>894.3007901052999</v>
       </c>
       <c r="I34" t="n">
-        <v>1027.323669041389</v>
+        <v>1027.323669041383</v>
       </c>
       <c r="J34" t="n">
-        <v>1300.29740969384</v>
+        <v>1300.297409693834</v>
       </c>
       <c r="K34" t="n">
-        <v>1322.551843630708</v>
+        <v>1322.551843630702</v>
       </c>
       <c r="L34" t="n">
-        <v>1208.867370744063</v>
+        <v>1322.551843630702</v>
       </c>
       <c r="M34" t="n">
-        <v>997.1182683172447</v>
+        <v>1322.551843630702</v>
       </c>
       <c r="N34" t="n">
-        <v>734.3050609721083</v>
+        <v>1188.583827665095</v>
       </c>
       <c r="O34" t="n">
-        <v>401.5317639225983</v>
+        <v>855.8105306155844</v>
       </c>
       <c r="P34" t="n">
-        <v>55.76000000000587</v>
+        <v>475.56012927389</v>
       </c>
       <c r="Q34" t="n">
-        <v>55.76000000000587</v>
+        <v>475.56012927389</v>
       </c>
       <c r="R34" t="n">
-        <v>55.76000000000587</v>
+        <v>55.76</v>
       </c>
       <c r="S34" t="n">
-        <v>55.76000000000587</v>
+        <v>55.76</v>
       </c>
       <c r="T34" t="n">
-        <v>155.7256791588107</v>
+        <v>155.7256791588049</v>
       </c>
       <c r="U34" t="n">
-        <v>314.1668717970974</v>
+        <v>314.1668717970915</v>
       </c>
       <c r="V34" t="n">
-        <v>424.8782646830434</v>
+        <v>424.8782646830375</v>
       </c>
       <c r="W34" t="n">
-        <v>508.6591829427208</v>
+        <v>508.6591829427149</v>
       </c>
       <c r="X34" t="n">
-        <v>571.5799739669143</v>
+        <v>571.5799739669084</v>
       </c>
       <c r="Y34" t="n">
-        <v>594.8792746459466</v>
+        <v>594.8792746459407</v>
       </c>
     </row>
     <row r="35">
@@ -6904,76 +6904,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>433.4059340141143</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C35" t="n">
-        <v>332.9265620514942</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D35" t="n">
-        <v>271.9779198900298</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E35" t="n">
-        <v>217.065506145718</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F35" t="n">
-        <v>161.6214367436858</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G35" t="n">
-        <v>107.3210606961947</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H35" t="n">
-        <v>48.7254458441468</v>
+        <v>44.72</v>
       </c>
       <c r="I35" t="n">
-        <v>44.72000000000588</v>
+        <v>44.72</v>
       </c>
       <c r="J35" t="n">
-        <v>44.72000000000588</v>
+        <v>44.72</v>
       </c>
       <c r="K35" t="n">
-        <v>44.72000000000588</v>
+        <v>179.7320762182563</v>
       </c>
       <c r="L35" t="n">
-        <v>44.72000000000588</v>
+        <v>733.1420762182562</v>
       </c>
       <c r="M35" t="n">
-        <v>555.5688287289408</v>
+        <v>1243.990904947191</v>
       </c>
       <c r="N35" t="n">
-        <v>1108.978828729013</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O35" t="n">
-        <v>1662.388828729086</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P35" t="n">
-        <v>2215.798828729159</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q35" t="n">
-        <v>2236.000000000294</v>
+        <v>2236</v>
       </c>
       <c r="R35" t="n">
-        <v>2236.000000000294</v>
+        <v>2236</v>
       </c>
       <c r="S35" t="n">
-        <v>2089.688719391887</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T35" t="n">
-        <v>1850.62247522162</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U35" t="n">
-        <v>1548.378741334135</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V35" t="n">
-        <v>1265.700939145424</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W35" t="n">
-        <v>974.4145997707292</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X35" t="n">
-        <v>729.685475062984</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y35" t="n">
-        <v>566.7385733631795</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="36">
@@ -6983,76 +6983,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>391.4553531635821</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C36" t="n">
-        <v>380.2433203903303</v>
+        <v>44.72</v>
       </c>
       <c r="D36" t="n">
-        <v>380.2433203903303</v>
+        <v>44.72</v>
       </c>
       <c r="E36" t="n">
-        <v>380.2433203903303</v>
+        <v>44.72</v>
       </c>
       <c r="F36" t="n">
-        <v>380.2433203903303</v>
+        <v>44.72</v>
       </c>
       <c r="G36" t="n">
-        <v>380.2433203903303</v>
+        <v>44.72</v>
       </c>
       <c r="H36" t="n">
-        <v>44.72000000000588</v>
+        <v>44.72</v>
       </c>
       <c r="I36" t="n">
-        <v>44.72000000000588</v>
+        <v>44.72</v>
       </c>
       <c r="J36" t="n">
-        <v>168.6765201753048</v>
+        <v>168.6765201752989</v>
       </c>
       <c r="K36" t="n">
-        <v>357.8693362696882</v>
+        <v>357.8693362696823</v>
       </c>
       <c r="L36" t="n">
-        <v>629.2197978648883</v>
+        <v>629.2197978648824</v>
       </c>
       <c r="M36" t="n">
-        <v>715.3003396077476</v>
+        <v>715.3003396077416</v>
       </c>
       <c r="N36" t="n">
-        <v>848.5806242153159</v>
+        <v>848.58062421531</v>
       </c>
       <c r="O36" t="n">
-        <v>1087.623075899035</v>
+        <v>1087.623075899029</v>
       </c>
       <c r="P36" t="n">
-        <v>1200.152420368541</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="Q36" t="n">
-        <v>1200.152420368541</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="R36" t="n">
-        <v>1000.885958457047</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S36" t="n">
-        <v>883.1445443513792</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T36" t="n">
-        <v>827.227609788234</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U36" t="n">
-        <v>776.5100746769342</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V36" t="n">
-        <v>711.3477845844895</v>
+        <v>357.8124310491301</v>
       </c>
       <c r="W36" t="n">
-        <v>628.1425897260769</v>
+        <v>274.6072361907175</v>
       </c>
       <c r="X36" t="n">
-        <v>476.2512616610173</v>
+        <v>204.0388125085078</v>
       </c>
       <c r="Y36" t="n">
-        <v>426.3609659376493</v>
+        <v>154.1485167851398</v>
       </c>
     </row>
     <row r="37">
@@ -7062,76 +7062,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>870.0458296400316</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C37" t="n">
-        <v>946.5478354584674</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D37" t="n">
-        <v>1010.366979583467</v>
+        <v>1018.077762255669</v>
       </c>
       <c r="E37" t="n">
-        <v>1078.695883794881</v>
+        <v>1086.406666467082</v>
       </c>
       <c r="F37" t="n">
-        <v>1153.556856386816</v>
+        <v>1161.267639059017</v>
       </c>
       <c r="G37" t="n">
-        <v>1257.463422273701</v>
+        <v>1265.174204945903</v>
       </c>
       <c r="H37" t="n">
-        <v>1377.480007433099</v>
+        <v>1385.1907901053</v>
       </c>
       <c r="I37" t="n">
-        <v>1549.112886369182</v>
+        <v>1556.823669041383</v>
       </c>
       <c r="J37" t="n">
-        <v>1860.696627021633</v>
+        <v>1860.696627021627</v>
       </c>
       <c r="K37" t="n">
-        <v>1921.561060958502</v>
+        <v>1921.561060958496</v>
       </c>
       <c r="L37" t="n">
-        <v>1847.270527465795</v>
+        <v>1847.270527465789</v>
       </c>
       <c r="M37" t="n">
-        <v>1674.915364432917</v>
+        <v>1674.915364432911</v>
       </c>
       <c r="N37" t="n">
-        <v>1451.49609648172</v>
+        <v>1451.496096481714</v>
       </c>
       <c r="O37" t="n">
-        <v>1158.116738826149</v>
+        <v>1158.116738826143</v>
       </c>
       <c r="P37" t="n">
-        <v>817.2602768783943</v>
+        <v>817.2602768783884</v>
       </c>
       <c r="Q37" t="n">
-        <v>437.6246542262751</v>
+        <v>437.6246542262692</v>
       </c>
       <c r="R37" t="n">
-        <v>57.2184643463245</v>
+        <v>57.21846434631862</v>
       </c>
       <c r="S37" t="n">
-        <v>44.72000000000588</v>
+        <v>44.72</v>
       </c>
       <c r="T37" t="n">
-        <v>175.5848964866036</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U37" t="n">
-        <v>372.6360891248902</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V37" t="n">
-        <v>521.9574820108362</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W37" t="n">
-        <v>644.3484002705136</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X37" t="n">
-        <v>745.8791912947071</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y37" t="n">
-        <v>807.7884919737394</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="38">
@@ -7141,76 +7141,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>433.4059340141143</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C38" t="n">
-        <v>332.9265620514942</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D38" t="n">
-        <v>271.9779198900298</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E38" t="n">
-        <v>217.065506145718</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F38" t="n">
-        <v>161.6214367436858</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G38" t="n">
-        <v>107.3210606961947</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H38" t="n">
-        <v>44.72000000000588</v>
+        <v>44.72</v>
       </c>
       <c r="I38" t="n">
-        <v>44.72000000000588</v>
+        <v>44.72</v>
       </c>
       <c r="J38" t="n">
-        <v>436.0291130376616</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K38" t="n">
-        <v>989.4391130377344</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L38" t="n">
-        <v>989.4391130377344</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M38" t="n">
-        <v>1500.28794176667</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N38" t="n">
-        <v>2053.697941766742</v>
+        <v>1500.287941766732</v>
       </c>
       <c r="O38" t="n">
-        <v>2236.000000000294</v>
+        <v>2053.697941766871</v>
       </c>
       <c r="P38" t="n">
-        <v>2236.000000000294</v>
+        <v>2053.697941766871</v>
       </c>
       <c r="Q38" t="n">
-        <v>2236.000000000294</v>
+        <v>2236</v>
       </c>
       <c r="R38" t="n">
-        <v>2236.000000000294</v>
+        <v>2236</v>
       </c>
       <c r="S38" t="n">
-        <v>2089.688719391887</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T38" t="n">
-        <v>1850.62247522162</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U38" t="n">
-        <v>1548.378741334135</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V38" t="n">
-        <v>1265.700939145424</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W38" t="n">
-        <v>974.4145997707292</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X38" t="n">
-        <v>729.685475062984</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y38" t="n">
-        <v>566.7385733631795</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="39">
@@ -7220,76 +7220,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>297.9507170509979</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C39" t="n">
-        <v>286.7386842777461</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="D39" t="n">
-        <v>286.7386842777461</v>
+        <v>44.72</v>
       </c>
       <c r="E39" t="n">
-        <v>286.7386842777461</v>
+        <v>44.72</v>
       </c>
       <c r="F39" t="n">
-        <v>44.72000000000588</v>
+        <v>44.72</v>
       </c>
       <c r="G39" t="n">
-        <v>44.72000000000588</v>
+        <v>44.72</v>
       </c>
       <c r="H39" t="n">
-        <v>44.72000000000588</v>
+        <v>44.72</v>
       </c>
       <c r="I39" t="n">
-        <v>44.72000000000588</v>
+        <v>44.72</v>
       </c>
       <c r="J39" t="n">
-        <v>168.6765201753048</v>
+        <v>168.6765201752989</v>
       </c>
       <c r="K39" t="n">
-        <v>357.8693362696882</v>
+        <v>357.8693362696823</v>
       </c>
       <c r="L39" t="n">
-        <v>629.2197978648883</v>
+        <v>629.2197978648824</v>
       </c>
       <c r="M39" t="n">
-        <v>715.3003396077476</v>
+        <v>715.3003396077416</v>
       </c>
       <c r="N39" t="n">
-        <v>848.5806242153159</v>
+        <v>848.58062421531</v>
       </c>
       <c r="O39" t="n">
-        <v>1087.623075899035</v>
+        <v>1087.623075899029</v>
       </c>
       <c r="P39" t="n">
-        <v>1200.152420368541</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="Q39" t="n">
-        <v>1025.324879873107</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="R39" t="n">
-        <v>826.0584179616131</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S39" t="n">
-        <v>708.3170038559451</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T39" t="n">
-        <v>652.4000692927999</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U39" t="n">
-        <v>601.6825341815002</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V39" t="n">
-        <v>536.5202440890555</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W39" t="n">
-        <v>453.3150492306428</v>
+        <v>274.6072361907174</v>
       </c>
       <c r="X39" t="n">
-        <v>382.7466255484332</v>
+        <v>204.0388125085078</v>
       </c>
       <c r="Y39" t="n">
-        <v>332.8563298250652</v>
+        <v>154.1485167851397</v>
       </c>
     </row>
     <row r="40">
@@ -7299,76 +7299,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>870.0458296400316</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C40" t="n">
-        <v>946.5478354584674</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D40" t="n">
-        <v>1010.366979583467</v>
+        <v>1018.077762255669</v>
       </c>
       <c r="E40" t="n">
-        <v>1078.695883794881</v>
+        <v>1086.406666467082</v>
       </c>
       <c r="F40" t="n">
-        <v>1153.556856386816</v>
+        <v>1161.267639059017</v>
       </c>
       <c r="G40" t="n">
-        <v>1257.463422273701</v>
+        <v>1265.174204945903</v>
       </c>
       <c r="H40" t="n">
-        <v>1377.480007433099</v>
+        <v>1377.480007433093</v>
       </c>
       <c r="I40" t="n">
-        <v>1549.112886369182</v>
+        <v>1549.112886369176</v>
       </c>
       <c r="J40" t="n">
-        <v>1860.696627021633</v>
+        <v>1860.696627021627</v>
       </c>
       <c r="K40" t="n">
-        <v>1921.561060958502</v>
+        <v>1921.561060958496</v>
       </c>
       <c r="L40" t="n">
-        <v>1847.270527465795</v>
+        <v>1847.270527465789</v>
       </c>
       <c r="M40" t="n">
-        <v>1674.915364432917</v>
+        <v>1674.915364432911</v>
       </c>
       <c r="N40" t="n">
-        <v>1451.49609648172</v>
+        <v>1451.496096481714</v>
       </c>
       <c r="O40" t="n">
-        <v>1158.116738826149</v>
+        <v>1158.116738826143</v>
       </c>
       <c r="P40" t="n">
-        <v>817.2602768783943</v>
+        <v>817.2602768783884</v>
       </c>
       <c r="Q40" t="n">
-        <v>437.6246542262751</v>
+        <v>437.6246542262692</v>
       </c>
       <c r="R40" t="n">
-        <v>57.2184643463245</v>
+        <v>57.21846434631862</v>
       </c>
       <c r="S40" t="n">
-        <v>44.72000000000588</v>
+        <v>44.72</v>
       </c>
       <c r="T40" t="n">
-        <v>175.5848964866036</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U40" t="n">
-        <v>372.6360891248902</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V40" t="n">
-        <v>521.9574820108362</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W40" t="n">
-        <v>644.3484002705136</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X40" t="n">
-        <v>745.8791912947071</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y40" t="n">
-        <v>807.7884919737394</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="41">
@@ -7378,76 +7378,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>433.4059340141143</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C41" t="n">
-        <v>332.9265620514942</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D41" t="n">
-        <v>271.9779198900298</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E41" t="n">
-        <v>217.065506145718</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F41" t="n">
-        <v>161.6214367436858</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G41" t="n">
-        <v>107.3210606961947</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H41" t="n">
-        <v>48.7254458441468</v>
+        <v>44.72</v>
       </c>
       <c r="I41" t="n">
-        <v>44.72000000000588</v>
+        <v>44.72</v>
       </c>
       <c r="J41" t="n">
-        <v>436.0291130376616</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K41" t="n">
-        <v>436.0291130376616</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L41" t="n">
-        <v>436.0291130376616</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M41" t="n">
-        <v>946.8779417665967</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N41" t="n">
-        <v>1500.28794176667</v>
+        <v>1500.287941766721</v>
       </c>
       <c r="O41" t="n">
-        <v>1797.400904947626</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P41" t="n">
-        <v>1797.400904947626</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q41" t="n">
-        <v>2236.000000000294</v>
+        <v>2236</v>
       </c>
       <c r="R41" t="n">
-        <v>2236.000000000294</v>
+        <v>2236</v>
       </c>
       <c r="S41" t="n">
-        <v>2089.688719391887</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T41" t="n">
-        <v>1850.62247522162</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U41" t="n">
-        <v>1548.378741334135</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V41" t="n">
-        <v>1265.700939145424</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W41" t="n">
-        <v>974.4145997707292</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X41" t="n">
-        <v>729.685475062984</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y41" t="n">
-        <v>566.7385733631795</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="42">
@@ -7457,76 +7457,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>407.3842417608361</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C42" t="n">
-        <v>396.1722089875843</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D42" t="n">
-        <v>44.72000000000588</v>
+        <v>110.1140157855959</v>
       </c>
       <c r="E42" t="n">
-        <v>44.72000000000588</v>
+        <v>110.1140157855959</v>
       </c>
       <c r="F42" t="n">
-        <v>44.72000000000588</v>
+        <v>44.72</v>
       </c>
       <c r="G42" t="n">
-        <v>44.72000000000588</v>
+        <v>44.72</v>
       </c>
       <c r="H42" t="n">
-        <v>44.72000000000588</v>
+        <v>44.72</v>
       </c>
       <c r="I42" t="n">
-        <v>44.72000000000588</v>
+        <v>44.72</v>
       </c>
       <c r="J42" t="n">
-        <v>168.6765201753048</v>
+        <v>168.6765201752989</v>
       </c>
       <c r="K42" t="n">
-        <v>357.8693362696882</v>
+        <v>357.8693362696823</v>
       </c>
       <c r="L42" t="n">
-        <v>629.2197978648883</v>
+        <v>629.2197978648824</v>
       </c>
       <c r="M42" t="n">
-        <v>715.3003396077476</v>
+        <v>715.3003396077416</v>
       </c>
       <c r="N42" t="n">
-        <v>848.5806242153159</v>
+        <v>848.58062421531</v>
       </c>
       <c r="O42" t="n">
-        <v>1087.623075899035</v>
+        <v>1087.623075899029</v>
       </c>
       <c r="P42" t="n">
-        <v>1200.152420368541</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="Q42" t="n">
-        <v>1200.152420368541</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="R42" t="n">
-        <v>935.4919426714513</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S42" t="n">
-        <v>817.7505285657833</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T42" t="n">
-        <v>761.8335940026381</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U42" t="n">
-        <v>711.1160588913383</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V42" t="n">
-        <v>645.9537687988936</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W42" t="n">
-        <v>562.748573940481</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X42" t="n">
-        <v>492.1801502582714</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y42" t="n">
-        <v>442.2898545349034</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="43">
@@ -7536,76 +7536,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>870.0458296400316</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C43" t="n">
-        <v>946.5478354584674</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D43" t="n">
-        <v>1010.366979583467</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E43" t="n">
-        <v>1078.695883794881</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F43" t="n">
-        <v>1153.556856386816</v>
+        <v>1153.55685638681</v>
       </c>
       <c r="G43" t="n">
-        <v>1257.463422273701</v>
+        <v>1257.463422273695</v>
       </c>
       <c r="H43" t="n">
-        <v>1377.480007433099</v>
+        <v>1377.480007433093</v>
       </c>
       <c r="I43" t="n">
-        <v>1549.112886369182</v>
+        <v>1549.112886369176</v>
       </c>
       <c r="J43" t="n">
-        <v>1860.696627021633</v>
+        <v>1860.696627021627</v>
       </c>
       <c r="K43" t="n">
-        <v>1921.561060958502</v>
+        <v>1921.561060958496</v>
       </c>
       <c r="L43" t="n">
-        <v>1847.270527465795</v>
+        <v>1847.270527465789</v>
       </c>
       <c r="M43" t="n">
-        <v>1674.915364432917</v>
+        <v>1674.915364432911</v>
       </c>
       <c r="N43" t="n">
-        <v>1451.49609648172</v>
+        <v>1451.496096481714</v>
       </c>
       <c r="O43" t="n">
-        <v>1158.116738826149</v>
+        <v>1158.116738826143</v>
       </c>
       <c r="P43" t="n">
-        <v>817.2602768783943</v>
+        <v>817.2602768783884</v>
       </c>
       <c r="Q43" t="n">
-        <v>437.6246542262751</v>
+        <v>437.6246542262692</v>
       </c>
       <c r="R43" t="n">
-        <v>57.2184643463245</v>
+        <v>57.21846434631862</v>
       </c>
       <c r="S43" t="n">
-        <v>44.72000000000588</v>
+        <v>44.72</v>
       </c>
       <c r="T43" t="n">
-        <v>175.5848964866036</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U43" t="n">
-        <v>372.6360891248902</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V43" t="n">
-        <v>521.9574820108362</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W43" t="n">
-        <v>644.3484002705136</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X43" t="n">
-        <v>745.8791912947071</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y43" t="n">
-        <v>807.7884919737394</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="44">
@@ -7615,76 +7615,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>433.4059340141143</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C44" t="n">
-        <v>332.9265620514942</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D44" t="n">
-        <v>271.9779198900298</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E44" t="n">
-        <v>217.065506145718</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F44" t="n">
-        <v>161.6214367436858</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G44" t="n">
-        <v>103.3156148520538</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H44" t="n">
-        <v>44.72000000000588</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I44" t="n">
-        <v>44.72000000000588</v>
+        <v>44.72</v>
       </c>
       <c r="J44" t="n">
-        <v>436.0291130376616</v>
+        <v>179.7320762182244</v>
       </c>
       <c r="K44" t="n">
-        <v>989.4391130377344</v>
+        <v>733.1420762182244</v>
       </c>
       <c r="L44" t="n">
-        <v>989.4391130377344</v>
+        <v>733.1420762182244</v>
       </c>
       <c r="M44" t="n">
-        <v>1500.28794176667</v>
+        <v>1243.990904947159</v>
       </c>
       <c r="N44" t="n">
-        <v>2053.697941766742</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O44" t="n">
-        <v>2053.697941766742</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P44" t="n">
-        <v>2053.697941766742</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q44" t="n">
-        <v>2236.000000000294</v>
+        <v>2236</v>
       </c>
       <c r="R44" t="n">
-        <v>2236.000000000294</v>
+        <v>2236</v>
       </c>
       <c r="S44" t="n">
-        <v>2089.688719391887</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T44" t="n">
-        <v>1850.62247522162</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U44" t="n">
-        <v>1548.378741334135</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V44" t="n">
-        <v>1265.700939145424</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W44" t="n">
-        <v>974.4145997707292</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X44" t="n">
-        <v>729.685475062984</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y44" t="n">
-        <v>566.7385733631795</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="45">
@@ -7694,76 +7694,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>472.778257546432</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C45" t="n">
-        <v>461.5662247731802</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="D45" t="n">
-        <v>461.5662247731802</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="E45" t="n">
-        <v>115.4327932358947</v>
+        <v>44.72</v>
       </c>
       <c r="F45" t="n">
-        <v>115.4327932358947</v>
+        <v>44.72</v>
       </c>
       <c r="G45" t="n">
-        <v>44.72000000000588</v>
+        <v>44.72</v>
       </c>
       <c r="H45" t="n">
-        <v>44.72000000000588</v>
+        <v>44.72</v>
       </c>
       <c r="I45" t="n">
-        <v>44.72000000000588</v>
+        <v>44.72</v>
       </c>
       <c r="J45" t="n">
-        <v>168.6765201753048</v>
+        <v>168.6765201752989</v>
       </c>
       <c r="K45" t="n">
-        <v>357.8693362696882</v>
+        <v>357.8693362696823</v>
       </c>
       <c r="L45" t="n">
-        <v>629.2197978648883</v>
+        <v>629.2197978648824</v>
       </c>
       <c r="M45" t="n">
-        <v>715.3003396077476</v>
+        <v>715.3003396077416</v>
       </c>
       <c r="N45" t="n">
-        <v>848.5806242153159</v>
+        <v>848.58062421531</v>
       </c>
       <c r="O45" t="n">
-        <v>1087.623075899035</v>
+        <v>1087.623075899029</v>
       </c>
       <c r="P45" t="n">
-        <v>1200.152420368541</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="Q45" t="n">
-        <v>1200.152420368541</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="R45" t="n">
-        <v>1000.885958457047</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S45" t="n">
-        <v>883.1445443513792</v>
+        <v>529.6091908160197</v>
       </c>
       <c r="T45" t="n">
-        <v>827.227609788234</v>
+        <v>473.6922562528744</v>
       </c>
       <c r="U45" t="n">
-        <v>776.5100746769342</v>
+        <v>422.9747211415747</v>
       </c>
       <c r="V45" t="n">
-        <v>711.3477845844895</v>
+        <v>357.8124310491301</v>
       </c>
       <c r="W45" t="n">
-        <v>628.1425897260769</v>
+        <v>274.6072361907174</v>
       </c>
       <c r="X45" t="n">
-        <v>557.5741660438673</v>
+        <v>204.0388125085078</v>
       </c>
       <c r="Y45" t="n">
-        <v>507.6838703204993</v>
+        <v>154.1485167851397</v>
       </c>
     </row>
     <row r="46">
@@ -7773,76 +7773,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>877.7566123122388</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C46" t="n">
-        <v>954.2586181306746</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D46" t="n">
-        <v>1010.366979583467</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E46" t="n">
-        <v>1078.695883794881</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F46" t="n">
-        <v>1153.556856386816</v>
+        <v>1153.55685638681</v>
       </c>
       <c r="G46" t="n">
-        <v>1257.463422273701</v>
+        <v>1257.463422273695</v>
       </c>
       <c r="H46" t="n">
-        <v>1377.480007433099</v>
+        <v>1377.480007433093</v>
       </c>
       <c r="I46" t="n">
-        <v>1549.112886369182</v>
+        <v>1549.112886369176</v>
       </c>
       <c r="J46" t="n">
-        <v>1860.696627021633</v>
+        <v>1860.696627021627</v>
       </c>
       <c r="K46" t="n">
-        <v>1921.561060958502</v>
+        <v>1921.561060958496</v>
       </c>
       <c r="L46" t="n">
-        <v>1847.270527465795</v>
+        <v>1847.270527465789</v>
       </c>
       <c r="M46" t="n">
-        <v>1674.915364432917</v>
+        <v>1674.915364432911</v>
       </c>
       <c r="N46" t="n">
-        <v>1451.49609648172</v>
+        <v>1451.496096481714</v>
       </c>
       <c r="O46" t="n">
-        <v>1158.116738826149</v>
+        <v>1158.116738826143</v>
       </c>
       <c r="P46" t="n">
-        <v>817.2602768783943</v>
+        <v>817.2602768783884</v>
       </c>
       <c r="Q46" t="n">
-        <v>437.6246542262751</v>
+        <v>437.6246542262692</v>
       </c>
       <c r="R46" t="n">
-        <v>57.2184643463245</v>
+        <v>57.21846434631862</v>
       </c>
       <c r="S46" t="n">
-        <v>44.72000000000588</v>
+        <v>44.72</v>
       </c>
       <c r="T46" t="n">
-        <v>183.2956791588107</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U46" t="n">
-        <v>380.3468717970974</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V46" t="n">
-        <v>529.6682646830434</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W46" t="n">
-        <v>652.0591829427208</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X46" t="n">
-        <v>753.5899739669143</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y46" t="n">
-        <v>815.4992746459466</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
   </sheetData>
@@ -7964,7 +7964,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -7976,7 +7976,7 @@
         <v>544.2621276423173</v>
       </c>
       <c r="N2" t="n">
-        <v>881.2388570597343</v>
+        <v>898.2489580698352</v>
       </c>
       <c r="O2" t="n">
         <v>491.2478695740924</v>
@@ -7985,7 +7985,7 @@
         <v>421.2870600406814</v>
       </c>
       <c r="Q2" t="n">
-        <v>593.8226843274854</v>
+        <v>181.5508529763179</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8210,19 +8210,19 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>552.9902962911499</v>
+        <v>965.2621276423173</v>
       </c>
       <c r="N5" t="n">
-        <v>477.2489580698352</v>
+        <v>898.2489580698352</v>
       </c>
       <c r="O5" t="n">
         <v>491.2478695740924</v>
       </c>
       <c r="P5" t="n">
-        <v>421.2870600406814</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q5" t="n">
-        <v>593.8226843274854</v>
+        <v>181.5508529763179</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8444,22 +8444,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>421</v>
       </c>
       <c r="M8" t="n">
-        <v>552.9902962911499</v>
+        <v>965.2621276423173</v>
       </c>
       <c r="N8" t="n">
         <v>898.2489580698352</v>
       </c>
       <c r="O8" t="n">
-        <v>491.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P8" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q8" t="n">
-        <v>593.8226843274854</v>
+        <v>181.5508529763179</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8678,10 +8678,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>559</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>1060.271045550332</v>
@@ -8912,10 +8912,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K14" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -8924,13 +8924,13 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N14" t="n">
-        <v>777.3630622928066</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O14" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2870600406814136</v>
+        <v>136.6628946047192</v>
       </c>
       <c r="Q14" t="n">
         <v>615.8520732695737</v>
@@ -9149,13 +9149,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K17" t="n">
-        <v>300.1141042229715</v>
+        <v>559</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>136.375834564038</v>
       </c>
       <c r="M17" t="n">
         <v>1060.271045550332</v>
@@ -9386,25 +9386,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>559.0000000000001</v>
       </c>
       <c r="M20" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N20" t="n">
-        <v>777.3630622928068</v>
+        <v>613.624792633873</v>
       </c>
       <c r="O20" t="n">
         <v>70.24786957409245</v>
       </c>
       <c r="P20" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q20" t="n">
         <v>615.8520732695737</v>
@@ -9626,10 +9626,10 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K23" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>559.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>1060.271045550332</v>
@@ -9638,13 +9638,13 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O23" t="n">
-        <v>70.24786957409245</v>
+        <v>206.6237041381304</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q23" t="n">
-        <v>193.2279078336117</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9863,7 +9863,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
-        <v>697.0000000000733</v>
+        <v>697</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -9872,16 +9872,16 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N26" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O26" t="n">
-        <v>767.2478695741659</v>
+        <v>602.4011407444422</v>
       </c>
       <c r="P26" t="n">
-        <v>11.82540668803892</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q26" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10097,13 +10097,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>697</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>484.3856125693276</v>
       </c>
       <c r="M29" t="n">
         <v>1060.271045550332</v>
@@ -10112,10 +10112,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O29" t="n">
-        <v>767.2478695741659</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P29" t="n">
-        <v>89.41094226915955</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q29" t="n">
         <v>615.8520732695737</v>
@@ -10334,7 +10334,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -10349,13 +10349,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O32" t="n">
-        <v>159.3717518025708</v>
+        <v>767.2478695740924</v>
       </c>
       <c r="P32" t="n">
-        <v>697.2870600407549</v>
+        <v>697.2870600406815</v>
       </c>
       <c r="Q32" t="n">
-        <v>615.8520732695737</v>
+        <v>403.2376858389012</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10574,25 +10574,25 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>136.3758345638952</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M35" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N35" t="n">
-        <v>1036.248958069909</v>
+        <v>1036.248958069978</v>
       </c>
       <c r="O35" t="n">
-        <v>629.2478695741659</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P35" t="n">
-        <v>559.2870600407549</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q35" t="n">
-        <v>193.2279078336825</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10811,7 +10811,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
-        <v>559.0000000000734</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -10820,16 +10820,16 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N38" t="n">
-        <v>1036.248958069909</v>
+        <v>1036.248958069978</v>
       </c>
       <c r="O38" t="n">
-        <v>254.3913627392961</v>
+        <v>629.2478695742327</v>
       </c>
       <c r="P38" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q38" t="n">
-        <v>172.8226843274854</v>
+        <v>356.9661774922619</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11057,10 +11057,10 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N41" t="n">
-        <v>1036.248958069909</v>
+        <v>1036.248958069966</v>
       </c>
       <c r="O41" t="n">
-        <v>370.3619737972811</v>
+        <v>370.3619737969327</v>
       </c>
       <c r="P41" t="n">
         <v>0.2870600406814136</v>
@@ -11282,10 +11282,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>430.3047365861567</v>
+        <v>171.4188408089534</v>
       </c>
       <c r="K44" t="n">
-        <v>559.0000000000734</v>
+        <v>559</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -11294,7 +11294,7 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N44" t="n">
-        <v>1036.248958069909</v>
+        <v>1036.24895807001</v>
       </c>
       <c r="O44" t="n">
         <v>70.24786957409245</v>
@@ -11303,7 +11303,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q44" t="n">
-        <v>356.9661774926891</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -24420,7 +24420,7 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>6.484208614300456</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -24474,7 +24474,7 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>6.484208614585384</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
@@ -24657,7 +24657,7 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>6.484208614382396</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -24696,7 +24696,7 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>6.48420861429733</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
@@ -24836,25 +24836,25 @@
         <v>112.5476281577792</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>209.6316114025499</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>126.79387791018</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>376.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>414.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>415.6021279811511</v>
       </c>
       <c r="S31" t="n">
-        <v>12.11393324286096</v>
+        <v>51.37347970285543</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -24894,7 +24894,7 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>6.484208614585469</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -24933,7 +24933,7 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>6.484208614300485</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
         <v>0</v>
@@ -25070,25 +25070,25 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>112.5476281577792</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>209.6316114025499</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>127.556739465733</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>34.13385104491095</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>414.839266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>415.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>51.37347970285543</v>
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8836646.701397901</v>
+        <v>8836646.701397881</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9795227.250538362</v>
+        <v>9795227.250538349</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10753807.79967884</v>
+        <v>10753807.7996788</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11723300.70048206</v>
+        <v>11723300.70048203</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>12699317.90673983</v>
+        <v>12699317.90673979</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13675335.11299759</v>
+        <v>13675335.11299756</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14651352.31925536</v>
+        <v>14651352.31925533</v>
       </c>
     </row>
   </sheetData>
@@ -26275,40 +26275,40 @@
         <v>1227892.61432428</v>
       </c>
       <c r="D2" t="n">
-        <v>1227892.614324279</v>
+        <v>1227892.61432428</v>
       </c>
       <c r="E2" t="n">
         <v>1227892.61432428</v>
       </c>
       <c r="F2" t="n">
-        <v>1227892.614324279</v>
+        <v>1227892.61432428</v>
       </c>
       <c r="G2" t="n">
         <v>1227892.61432428</v>
       </c>
       <c r="H2" t="n">
+        <v>1227892.61432428</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1227892.61432428</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1205956.174725086</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1205956.174725109</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1205956.174725086</v>
+      </c>
+      <c r="M2" t="n">
         <v>1227892.614324279</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1227892.614324279</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1205956.174725109</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1205956.174725102</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1205956.174725109</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1227892.61432428</v>
       </c>
       <c r="N2" t="n">
         <v>1227892.61432428</v>
       </c>
       <c r="O2" t="n">
-        <v>1227892.614324279</v>
+        <v>1227892.61432428</v>
       </c>
       <c r="P2" t="n">
         <v>1227892.61432428</v>
@@ -26345,7 +26345,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>445568.0000000258</v>
+        <v>445568</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>566354.9592425094</v>
+        <v>567917.5723359545</v>
       </c>
       <c r="C4" t="n">
-        <v>564322.4434789647</v>
+        <v>565885.0565724098</v>
       </c>
       <c r="D4" t="n">
-        <v>562287.1704809261</v>
+        <v>563849.7835743711</v>
       </c>
       <c r="E4" t="n">
-        <v>543094.0532265352</v>
+        <v>544835.9030396428</v>
       </c>
       <c r="F4" t="n">
-        <v>541151.157881031</v>
+        <v>542893.0076941387</v>
       </c>
       <c r="G4" t="n">
-        <v>539205.5814128454</v>
+        <v>540947.431225953</v>
       </c>
       <c r="H4" t="n">
-        <v>537257.3045955442</v>
+        <v>538999.1544086519</v>
       </c>
       <c r="I4" t="n">
-        <v>535306.307952184</v>
+        <v>537048.1577652916</v>
       </c>
       <c r="J4" t="n">
-        <v>503977.1710046672</v>
+        <v>505898.2575374336</v>
       </c>
       <c r="K4" t="n">
-        <v>502172.4589193104</v>
+        <v>504093.5454520936</v>
       </c>
       <c r="L4" t="n">
-        <v>500365.1826816191</v>
+        <v>502286.2692143855</v>
       </c>
       <c r="M4" t="n">
-        <v>527474.7245420919</v>
+        <v>529216.5743552083</v>
       </c>
       <c r="N4" t="n">
-        <v>525509.8275072386</v>
+        <v>527251.677320355</v>
       </c>
       <c r="O4" t="n">
-        <v>523542.0882495004</v>
+        <v>525283.9380626167</v>
       </c>
       <c r="P4" t="n">
-        <v>521571.4853984903</v>
+        <v>523313.3352116066</v>
       </c>
     </row>
     <row r="5">
@@ -26449,25 +26449,25 @@
         <v>63411.35</v>
       </c>
       <c r="J5" t="n">
-        <v>68523.05900000446</v>
+        <v>68523.05900000001</v>
       </c>
       <c r="K5" t="n">
-        <v>68523.05900000446</v>
+        <v>68523.05900000001</v>
       </c>
       <c r="L5" t="n">
-        <v>68523.05900000446</v>
+        <v>68523.05900000001</v>
       </c>
       <c r="M5" t="n">
-        <v>63411.35000000447</v>
+        <v>63411.35</v>
       </c>
       <c r="N5" t="n">
-        <v>63411.35000000447</v>
+        <v>63411.35</v>
       </c>
       <c r="O5" t="n">
-        <v>63411.35000000447</v>
+        <v>63411.35</v>
       </c>
       <c r="P5" t="n">
-        <v>63411.35000000447</v>
+        <v>63411.35</v>
       </c>
     </row>
     <row r="6">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>454121.2550817704</v>
+        <v>452558.6419883253</v>
       </c>
       <c r="C6" t="n">
-        <v>604345.7708453153</v>
+        <v>602783.15775187</v>
       </c>
       <c r="D6" t="n">
-        <v>606381.0438433533</v>
+        <v>604818.4307499084</v>
       </c>
       <c r="E6" t="n">
-        <v>292811.2110977444</v>
+        <v>291069.361284637</v>
       </c>
       <c r="F6" t="n">
-        <v>623330.1064432483</v>
+        <v>621588.2566301409</v>
       </c>
       <c r="G6" t="n">
-        <v>625275.6829114342</v>
+        <v>623533.8330983266</v>
       </c>
       <c r="H6" t="n">
-        <v>627223.9597287351</v>
+        <v>625482.1099156277</v>
       </c>
       <c r="I6" t="n">
-        <v>629174.9563720954</v>
+        <v>627433.1065589882</v>
       </c>
       <c r="J6" t="n">
-        <v>187887.9447204113</v>
+        <v>185966.8581876523</v>
       </c>
       <c r="K6" t="n">
-        <v>635260.6568057869</v>
+        <v>633339.5702730149</v>
       </c>
       <c r="L6" t="n">
-        <v>637067.933043485</v>
+        <v>635146.8465107009</v>
       </c>
       <c r="M6" t="n">
-        <v>605806.5397821831</v>
+        <v>604064.6899690708</v>
       </c>
       <c r="N6" t="n">
-        <v>638971.4368170365</v>
+        <v>637229.5870039247</v>
       </c>
       <c r="O6" t="n">
-        <v>392139.1760747745</v>
+        <v>390397.3262616631</v>
       </c>
       <c r="P6" t="n">
-        <v>642909.7789257847</v>
+        <v>641167.9291126734</v>
       </c>
     </row>
   </sheetData>
@@ -26883,25 +26883,25 @@
         <v>559</v>
       </c>
       <c r="J4" t="n">
-        <v>697.0000000000734</v>
+        <v>697</v>
       </c>
       <c r="K4" t="n">
-        <v>697.0000000000734</v>
+        <v>697</v>
       </c>
       <c r="L4" t="n">
-        <v>697.0000000000734</v>
+        <v>697</v>
       </c>
       <c r="M4" t="n">
-        <v>559.0000000000734</v>
+        <v>559</v>
       </c>
       <c r="N4" t="n">
-        <v>559.0000000000734</v>
+        <v>559</v>
       </c>
       <c r="O4" t="n">
-        <v>559.0000000000734</v>
+        <v>559</v>
       </c>
       <c r="P4" t="n">
-        <v>559.0000000000734</v>
+        <v>559</v>
       </c>
     </row>
   </sheetData>
@@ -26984,7 +26984,7 @@
         <v>350</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>-0</v>
@@ -27002,7 +27002,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>39</v>
@@ -27024,10 +27024,10 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
         <v>-0</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -27091,7 +27091,7 @@
         <v>-0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>-0</v>
@@ -27100,7 +27100,7 @@
         <v>-0</v>
       </c>
       <c r="J4" t="n">
-        <v>559.0000000000664</v>
+        <v>559</v>
       </c>
       <c r="K4" t="n">
         <v>-0</v>
@@ -27433,7 +27433,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>231.5850086145855</v>
+        <v>400</v>
       </c>
       <c r="C2" t="n">
         <v>400</v>
@@ -27481,7 +27481,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>250.8785988282945</v>
+        <v>82.46360744287983</v>
       </c>
       <c r="S2" t="n">
         <v>400</v>
@@ -27515,7 +27515,7 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
-        <v>161.2819111235451</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
         <v>347.9376868977026</v>
@@ -27527,10 +27527,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I3" t="n">
         <v>217.1263858913485</v>
@@ -27557,19 +27557,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>400</v>
       </c>
       <c r="S3" t="n">
-        <v>400</v>
+        <v>45.5639999646113</v>
       </c>
       <c r="T3" t="n">
         <v>400</v>
       </c>
       <c r="U3" t="n">
-        <v>400</v>
+        <v>69.78964074244544</v>
       </c>
       <c r="V3" t="n">
         <v>400</v>
@@ -27612,13 +27612,13 @@
         <v>400</v>
       </c>
       <c r="I4" t="n">
+        <v>176.6334556201183</v>
+      </c>
+      <c r="J4" t="n">
+        <v>35.26894883590776</v>
+      </c>
+      <c r="K4" t="n">
         <v>400</v>
-      </c>
-      <c r="J4" t="n">
-        <v>400</v>
-      </c>
-      <c r="K4" t="n">
-        <v>301.0451253455172</v>
       </c>
       <c r="L4" t="n">
         <v>400</v>
@@ -27642,22 +27642,22 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>362.3734797028554</v>
+        <v>400</v>
       </c>
       <c r="T4" t="n">
-        <v>210.0245665062577</v>
+        <v>308.1547227449278</v>
       </c>
       <c r="U4" t="n">
         <v>150.9583912744579</v>
       </c>
       <c r="V4" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W4" t="n">
         <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y4" t="n">
         <v>287.4653528494624</v>
@@ -27755,13 +27755,13 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>172.5204020740694</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>325.7395358750273</v>
@@ -27794,10 +27794,10 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R6" t="n">
-        <v>126.2737972923793</v>
+        <v>400</v>
       </c>
       <c r="S6" t="n">
         <v>400</v>
@@ -27809,7 +27809,7 @@
         <v>400</v>
       </c>
       <c r="V6" t="n">
-        <v>337.0175303123801</v>
+        <v>400</v>
       </c>
       <c r="W6" t="n">
         <v>400</v>
@@ -27828,22 +27828,22 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>287.1138003370787</v>
+      </c>
+      <c r="C7" t="n">
         <v>400</v>
       </c>
-      <c r="C7" t="n">
-        <v>272.7252466480447</v>
-      </c>
       <c r="D7" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E7" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F7" t="n">
         <v>274.3828559677419</v>
       </c>
       <c r="G7" t="n">
-        <v>245.04387284153</v>
+        <v>400</v>
       </c>
       <c r="H7" t="n">
         <v>400</v>
@@ -27879,16 +27879,16 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>400</v>
+        <v>362.3734797028554</v>
       </c>
       <c r="T7" t="n">
-        <v>400</v>
+        <v>210.0245665062577</v>
       </c>
       <c r="U7" t="n">
-        <v>400</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V7" t="n">
-        <v>400</v>
+        <v>376.2108647381414</v>
       </c>
       <c r="W7" t="n">
         <v>400</v>
@@ -27897,7 +27897,7 @@
         <v>400</v>
       </c>
       <c r="Y7" t="n">
-        <v>302.3948601767042</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8">
@@ -27907,7 +27907,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>400</v>
+        <v>231.5850086145855</v>
       </c>
       <c r="C8" t="n">
         <v>400</v>
@@ -27967,7 +27967,7 @@
         <v>400</v>
       </c>
       <c r="V8" t="n">
-        <v>231.5850086145855</v>
+        <v>400</v>
       </c>
       <c r="W8" t="n">
         <v>400</v>
@@ -28031,13 +28031,13 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R9" t="n">
+        <v>126.2737972923793</v>
+      </c>
+      <c r="S9" t="n">
         <v>400</v>
-      </c>
-      <c r="S9" t="n">
-        <v>103.9804977972282</v>
       </c>
       <c r="T9" t="n">
         <v>400</v>
@@ -28049,10 +28049,10 @@
         <v>400</v>
       </c>
       <c r="W9" t="n">
-        <v>11.37314290982852</v>
+        <v>216.0005783241979</v>
       </c>
       <c r="X9" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>399.3913927661343</v>
@@ -28065,10 +28065,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C10" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D10" t="n">
         <v>400</v>
@@ -28089,10 +28089,10 @@
         <v>400</v>
       </c>
       <c r="J10" t="n">
-        <v>136.5263263343255</v>
+        <v>35.26894883590776</v>
       </c>
       <c r="K10" t="n">
-        <v>288.520773801143</v>
+        <v>400</v>
       </c>
       <c r="L10" t="n">
         <v>400</v>
@@ -28116,10 +28116,10 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>362.3734797028554</v>
+        <v>363.0586544920345</v>
       </c>
       <c r="T10" t="n">
-        <v>400</v>
+        <v>210.0245665062577</v>
       </c>
       <c r="U10" t="n">
         <v>150.9583912744579</v>
@@ -28128,13 +28128,13 @@
         <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
         <v>400</v>
       </c>
       <c r="Y10" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11">
@@ -28235,10 +28235,10 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F12" t="n">
-        <v>339.6362423378769</v>
+        <v>252.6980156874616</v>
       </c>
       <c r="G12" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>332.1680871864211</v>
@@ -28271,10 +28271,10 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="S12" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
       <c r="T12" t="n">
         <v>350</v>
@@ -28393,7 +28393,7 @@
         <v>350</v>
       </c>
       <c r="F14" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="G14" t="n">
         <v>350</v>
@@ -28432,7 +28432,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S14" t="n">
-        <v>346.0346086145856</v>
+        <v>350</v>
       </c>
       <c r="T14" t="n">
         <v>350</v>
@@ -28469,16 +28469,16 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E15" t="n">
-        <v>269.6305770343469</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G15" t="n">
-        <v>325.7395358750273</v>
+        <v>245.2298605360059</v>
       </c>
       <c r="H15" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>217.1263858913485</v>
@@ -28666,10 +28666,10 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S17" t="n">
-        <v>346.0346086145856</v>
+        <v>350</v>
       </c>
       <c r="T17" t="n">
         <v>350</v>
@@ -28700,16 +28700,16 @@
         <v>350</v>
       </c>
       <c r="C18" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="D18" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E18" t="n">
-        <v>269.6305770343469</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G18" t="n">
         <v>325.7395358750273</v>
@@ -28745,7 +28745,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R18" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>350</v>
@@ -28903,10 +28903,10 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S20" t="n">
-        <v>350</v>
+        <v>346.0346086145856</v>
       </c>
       <c r="T20" t="n">
         <v>350</v>
@@ -28940,7 +28940,7 @@
         <v>350</v>
       </c>
       <c r="D21" t="n">
-        <v>285.2599243722602</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E21" t="n">
         <v>342.6720972219126</v>
@@ -28985,7 +28985,7 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="T21" t="n">
         <v>350</v>
@@ -29110,7 +29110,7 @@
         <v>350</v>
       </c>
       <c r="H23" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="I23" t="n">
         <v>150.0811596826846</v>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S23" t="n">
         <v>350</v>
@@ -29174,7 +29174,7 @@
         <v>350</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="D24" t="n">
         <v>347.9376868977026</v>
@@ -29186,10 +29186,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G24" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>332.1680871864211</v>
+        <v>245.2298605360059</v>
       </c>
       <c r="I24" t="n">
         <v>217.1263858913485</v>
@@ -29219,7 +29219,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R24" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="S24" t="n">
         <v>350</v>
@@ -29435,7 +29435,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>112.7189949938764</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -29453,7 +29453,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>173.0792650904796</v>
+        <v>285.7982600843558</v>
       </c>
       <c r="R27" t="n">
         <v>311</v>
@@ -29587,7 +29587,7 @@
         <v>311</v>
       </c>
       <c r="I29" t="n">
-        <v>150.0811596826846</v>
+        <v>150.0811596829788</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -29614,7 +29614,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>250.8785988282109</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S29" t="n">
         <v>311</v>
@@ -29690,7 +29690,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>285.7982600843561</v>
+        <v>285.7982600843558</v>
       </c>
       <c r="R30" t="n">
         <v>311</v>
@@ -29903,7 +29903,7 @@
         <v>311</v>
       </c>
       <c r="I33" t="n">
-        <v>217.1263858913485</v>
+        <v>311</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -29927,7 +29927,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>285.7982600843561</v>
+        <v>191.9246459757046</v>
       </c>
       <c r="R33" t="n">
         <v>311</v>
@@ -30061,7 +30061,7 @@
         <v>350</v>
       </c>
       <c r="I35" t="n">
-        <v>146.1157682969851</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -30103,7 +30103,7 @@
         <v>350</v>
       </c>
       <c r="W35" t="n">
-        <v>350</v>
+        <v>346.0346086145854</v>
       </c>
       <c r="X35" t="n">
         <v>350</v>
@@ -30122,7 +30122,7 @@
         <v>350</v>
       </c>
       <c r="C36" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="D36" t="n">
         <v>347.9376868977026</v>
@@ -30137,7 +30137,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I36" t="n">
         <v>217.1263858913485</v>
@@ -30179,13 +30179,13 @@
         <v>350</v>
       </c>
       <c r="V36" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
         <v>350</v>
       </c>
       <c r="X36" t="n">
-        <v>269.4903246609786</v>
+        <v>350</v>
       </c>
       <c r="Y36" t="n">
         <v>350</v>
@@ -30222,7 +30222,7 @@
         <v>350</v>
       </c>
       <c r="J37" t="n">
-        <v>350</v>
+        <v>342.2113306341341</v>
       </c>
       <c r="K37" t="n">
         <v>350</v>
@@ -30252,7 +30252,7 @@
         <v>350</v>
       </c>
       <c r="T37" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U37" t="n">
         <v>350</v>
@@ -30295,7 +30295,7 @@
         <v>350</v>
       </c>
       <c r="H38" t="n">
-        <v>346.0346086143005</v>
+        <v>350</v>
       </c>
       <c r="I38" t="n">
         <v>150.0811596826846</v>
@@ -30328,7 +30328,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S38" t="n">
-        <v>350</v>
+        <v>346.0346086145856</v>
       </c>
       <c r="T38" t="n">
         <v>350</v>
@@ -30362,13 +30362,13 @@
         <v>350</v>
       </c>
       <c r="D39" t="n">
-        <v>347.9376868977026</v>
+        <v>285.2599243722602</v>
       </c>
       <c r="E39" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
-        <v>100.037744902914</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G39" t="n">
         <v>325.7395358750273</v>
@@ -30401,7 +30401,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R39" t="n">
         <v>350</v>
@@ -30419,7 +30419,7 @@
         <v>350</v>
       </c>
       <c r="W39" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
         <v>350</v>
@@ -30453,7 +30453,7 @@
         <v>350</v>
       </c>
       <c r="H40" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="I40" t="n">
         <v>350</v>
@@ -30489,7 +30489,7 @@
         <v>350</v>
       </c>
       <c r="T40" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U40" t="n">
         <v>350</v>
@@ -30532,10 +30532,10 @@
         <v>350</v>
       </c>
       <c r="H41" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="I41" t="n">
-        <v>146.1157682969851</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -30605,7 +30605,7 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F42" t="n">
-        <v>339.6362423378769</v>
+        <v>274.8961667101369</v>
       </c>
       <c r="G42" t="n">
         <v>325.7395358750273</v>
@@ -30641,7 +30641,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R42" t="n">
-        <v>285.25992437226</v>
+        <v>350</v>
       </c>
       <c r="S42" t="n">
         <v>350</v>
@@ -30726,13 +30726,13 @@
         <v>350</v>
       </c>
       <c r="T43" t="n">
+        <v>350</v>
+      </c>
+      <c r="U43" t="n">
+        <v>350</v>
+      </c>
+      <c r="V43" t="n">
         <v>342.2113306341342</v>
-      </c>
-      <c r="U43" t="n">
-        <v>350</v>
-      </c>
-      <c r="V43" t="n">
-        <v>350</v>
       </c>
       <c r="W43" t="n">
         <v>350</v>
@@ -30766,13 +30766,13 @@
         <v>350</v>
       </c>
       <c r="G44" t="n">
-        <v>346.0346086143005</v>
+        <v>350</v>
       </c>
       <c r="H44" t="n">
         <v>350</v>
       </c>
       <c r="I44" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -30839,13 +30839,13 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>279.9943346964702</v>
       </c>
       <c r="F45" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G45" t="n">
-        <v>255.7338705714974</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H45" t="n">
         <v>332.1680871864211</v>
@@ -30881,7 +30881,7 @@
         <v>350</v>
       </c>
       <c r="S45" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
         <v>350</v>
@@ -30915,55 +30915,55 @@
         <v>350</v>
       </c>
       <c r="D46" t="n">
+        <v>350</v>
+      </c>
+      <c r="E46" t="n">
+        <v>350</v>
+      </c>
+      <c r="F46" t="n">
+        <v>350</v>
+      </c>
+      <c r="G46" t="n">
+        <v>350</v>
+      </c>
+      <c r="H46" t="n">
+        <v>350</v>
+      </c>
+      <c r="I46" t="n">
+        <v>350</v>
+      </c>
+      <c r="J46" t="n">
+        <v>350</v>
+      </c>
+      <c r="K46" t="n">
+        <v>350</v>
+      </c>
+      <c r="L46" t="n">
+        <v>350</v>
+      </c>
+      <c r="M46" t="n">
+        <v>350</v>
+      </c>
+      <c r="N46" t="n">
+        <v>350</v>
+      </c>
+      <c r="O46" t="n">
+        <v>350</v>
+      </c>
+      <c r="P46" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>350</v>
+      </c>
+      <c r="R46" t="n">
+        <v>350</v>
+      </c>
+      <c r="S46" t="n">
+        <v>350</v>
+      </c>
+      <c r="T46" t="n">
         <v>342.2113306341342</v>
-      </c>
-      <c r="E46" t="n">
-        <v>350</v>
-      </c>
-      <c r="F46" t="n">
-        <v>350</v>
-      </c>
-      <c r="G46" t="n">
-        <v>350</v>
-      </c>
-      <c r="H46" t="n">
-        <v>350</v>
-      </c>
-      <c r="I46" t="n">
-        <v>350</v>
-      </c>
-      <c r="J46" t="n">
-        <v>350</v>
-      </c>
-      <c r="K46" t="n">
-        <v>350</v>
-      </c>
-      <c r="L46" t="n">
-        <v>350</v>
-      </c>
-      <c r="M46" t="n">
-        <v>350</v>
-      </c>
-      <c r="N46" t="n">
-        <v>350</v>
-      </c>
-      <c r="O46" t="n">
-        <v>350</v>
-      </c>
-      <c r="P46" t="n">
-        <v>350</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>350</v>
-      </c>
-      <c r="R46" t="n">
-        <v>350</v>
-      </c>
-      <c r="S46" t="n">
-        <v>350</v>
-      </c>
-      <c r="T46" t="n">
-        <v>350</v>
       </c>
       <c r="U46" t="n">
         <v>350</v>
@@ -34743,7 +34743,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -34755,7 +34755,7 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>403.989898989899</v>
+        <v>421</v>
       </c>
       <c r="O2" t="n">
         <v>421</v>
@@ -34764,7 +34764,7 @@
         <v>421</v>
       </c>
       <c r="Q2" t="n">
-        <v>421</v>
+        <v>8.728168648832536</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34898,13 +34898,13 @@
         <v>171.2288738983814</v>
       </c>
       <c r="I4" t="n">
-        <v>223.3665443798817</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>364.7310511640923</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>12.52435154437416</v>
+        <v>111.479226198857</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34928,22 +34928,22 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>37.62652029714457</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>98.13015623867004</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -34989,19 +34989,19 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>8.728168648832595</v>
+        <v>421</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>421</v>
       </c>
       <c r="O5" t="n">
         <v>421</v>
       </c>
       <c r="P5" t="n">
-        <v>421</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>421</v>
+        <v>8.728168648832536</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35114,22 +35114,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H7" t="n">
         <v>171.2288738983814</v>
@@ -35165,16 +35165,16 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>189.9754334937423</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>200.8296897837838</v>
+        <v>177.0405545219251</v>
       </c>
       <c r="W7" t="n">
         <v>173.6271901612903</v>
@@ -35183,7 +35183,7 @@
         <v>152.5563545698924</v>
       </c>
       <c r="Y7" t="n">
-        <v>14.92950732724189</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="8">
@@ -35223,22 +35223,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>421</v>
       </c>
       <c r="M8" t="n">
-        <v>8.728168648832595</v>
+        <v>421</v>
       </c>
       <c r="N8" t="n">
         <v>421</v>
       </c>
       <c r="O8" t="n">
-        <v>421</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>421</v>
+        <v>8.728168648832536</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35351,10 +35351,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
         <v>114.4637819444445</v>
@@ -35375,10 +35375,10 @@
         <v>223.3665443798817</v>
       </c>
       <c r="J10" t="n">
-        <v>101.2573774984177</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>111.479226198857</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -35402,10 +35402,10 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>0.685174789179112</v>
       </c>
       <c r="T10" t="n">
-        <v>189.9754334937423</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -35414,13 +35414,13 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="11">
@@ -35457,10 +35457,10 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>559</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>516.0089179080152</v>
@@ -35691,10 +35691,10 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -35703,13 +35703,13 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N14" t="n">
-        <v>300.1141042229714</v>
+        <v>559</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>136.3758345640378</v>
       </c>
       <c r="Q14" t="n">
         <v>443.0293889420883</v>
@@ -35928,13 +35928,13 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>300.1141042229715</v>
+        <v>559</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>136.375834564038</v>
       </c>
       <c r="M17" t="n">
         <v>516.0089179080152</v>
@@ -36165,25 +36165,25 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>559.0000000000001</v>
       </c>
       <c r="M20" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N20" t="n">
-        <v>300.1141042229716</v>
+        <v>136.3758345640378</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>443.0293889420883</v>
@@ -36405,10 +36405,10 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>559.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>516.0089179080152</v>
@@ -36417,13 +36417,13 @@
         <v>559</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>136.375834564038</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="Q23" t="n">
-        <v>20.40522350612631</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36642,7 +36642,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K26" t="n">
-        <v>697.0000000000733</v>
+        <v>697</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -36651,16 +36651,16 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O26" t="n">
-        <v>697.0000000000734</v>
+        <v>532.1532711703497</v>
       </c>
       <c r="P26" t="n">
-        <v>11.5383466473575</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36721,7 +36721,7 @@
         <v>125.2086062376757</v>
       </c>
       <c r="K27" t="n">
-        <v>303.8228496346677</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L27" t="n">
         <v>274.091375348687</v>
@@ -36739,7 +36739,7 @@
         <v>113.6660045146532</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>112.7189949938763</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -36873,16 +36873,16 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>2.942149330001393e-10</v>
       </c>
       <c r="J29" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>697</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>484.3856125693276</v>
       </c>
       <c r="M29" t="n">
         <v>516.0089179080152</v>
@@ -36891,16 +36891,16 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O29" t="n">
-        <v>697.0000000000734</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>89.12388222847812</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>443.0293889420883</v>
       </c>
       <c r="R29" t="n">
-        <v>-8.360001804175401e-11</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -36976,7 +36976,7 @@
         <v>113.6660045146532</v>
       </c>
       <c r="Q30" t="n">
-        <v>112.7189949938765</v>
+        <v>112.7189949938763</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -37113,7 +37113,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -37128,13 +37128,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O32" t="n">
-        <v>89.12388222847837</v>
+        <v>697</v>
       </c>
       <c r="P32" t="n">
-        <v>697.0000000000734</v>
+        <v>697</v>
       </c>
       <c r="Q32" t="n">
-        <v>443.0293889420883</v>
+        <v>230.4150015114158</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37189,7 +37189,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>93.87361410865147</v>
       </c>
       <c r="J33" t="n">
         <v>125.2086062376757</v>
@@ -37213,7 +37213,7 @@
         <v>113.6660045146532</v>
       </c>
       <c r="Q33" t="n">
-        <v>112.7189949938765</v>
+        <v>18.84538088522502</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37353,25 +37353,25 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>136.3758345638952</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M35" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N35" t="n">
-        <v>559.0000000000734</v>
+        <v>559.0000000001428</v>
       </c>
       <c r="O35" t="n">
-        <v>559.0000000000734</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>559.0000000000734</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>20.40522350619705</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37508,7 +37508,7 @@
         <v>173.3665443798817</v>
       </c>
       <c r="J37" t="n">
-        <v>314.7310511640923</v>
+        <v>306.9423817982264</v>
       </c>
       <c r="K37" t="n">
         <v>61.47922619885696</v>
@@ -37538,7 +37538,7 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U37" t="n">
         <v>199.0416087255421</v>
@@ -37590,7 +37590,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K38" t="n">
-        <v>559.0000000000734</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -37599,16 +37599,16 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N38" t="n">
-        <v>559.0000000000734</v>
+        <v>559.0000000001428</v>
       </c>
       <c r="O38" t="n">
-        <v>184.1434931652037</v>
+        <v>559.0000000001403</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>184.1434931647765</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37739,7 +37739,7 @@
         <v>104.95612715847</v>
       </c>
       <c r="H40" t="n">
-        <v>121.2288738983814</v>
+        <v>113.4402045325156</v>
       </c>
       <c r="I40" t="n">
         <v>173.3665443798817</v>
@@ -37775,7 +37775,7 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U40" t="n">
         <v>199.0416087255421</v>
@@ -37836,10 +37836,10 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N41" t="n">
-        <v>559.0000000000734</v>
+        <v>559.0000000001312</v>
       </c>
       <c r="O41" t="n">
-        <v>300.1141042231886</v>
+        <v>300.1141042228402</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
@@ -38012,13 +38012,13 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U43" t="n">
         <v>199.0416087255421</v>
       </c>
       <c r="V43" t="n">
-        <v>150.8296897837838</v>
+        <v>143.041020417918</v>
       </c>
       <c r="W43" t="n">
         <v>123.6271901612903</v>
@@ -38061,10 +38061,10 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>395.2617303410664</v>
+        <v>136.3758345638631</v>
       </c>
       <c r="K44" t="n">
-        <v>559.0000000000734</v>
+        <v>559</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -38073,7 +38073,7 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N44" t="n">
-        <v>559.0000000000734</v>
+        <v>559.0000000001749</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -38082,7 +38082,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>184.1434931652037</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38201,7 +38201,7 @@
         <v>77.27475335195533</v>
       </c>
       <c r="D46" t="n">
-        <v>56.67511257857869</v>
+        <v>64.46378194444452</v>
       </c>
       <c r="E46" t="n">
         <v>69.01909516304346</v>
@@ -38249,7 +38249,7 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U46" t="n">
         <v>199.0416087255421</v>
